--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>223525</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>10.1899995803833</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>10.0200004577637</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>10.0699996948242</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>221469</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>10.1300001144409</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>10.1800003051758</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>325154</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>10.289999961853</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>10.1800003051758</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>374712</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>10.5299997329712</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>10.1099996566772</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>10.1099996566772</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>10.3800001144409</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>220499</v>
+        <v>114154</v>
       </c>
       <c r="C2715" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="D2715" t="n">
+        <v>10.0200004577637</v>
+      </c>
+      <c r="E2715" t="n">
         <v>10.0699996948242</v>
       </c>
-      <c r="D2715" t="n">
-        <v>9.875</v>
-      </c>
-      <c r="E2715" t="n">
-        <v>9.94999980926514</v>
-      </c>
       <c r="F2715" t="n">
-        <v>9.97500038146973</v>
+        <v>10.0600004196167</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>271284</v>
+        <v>220499</v>
       </c>
       <c r="C2716" t="n">
-        <v>10.0799999237061</v>
+        <v>10.0699996948242</v>
       </c>
       <c r="D2716" t="n">
-        <v>9.84000015258789</v>
+        <v>9.875</v>
       </c>
       <c r="E2716" t="n">
-        <v>9.90999984741211</v>
+        <v>9.94999980926514</v>
       </c>
       <c r="F2716" t="n">
-        <v>10</v>
+        <v>9.97500038146973</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>527400</v>
+        <v>271284</v>
       </c>
       <c r="C2717" t="n">
-        <v>10.2799997329712</v>
+        <v>10.0799999237061</v>
       </c>
       <c r="D2717" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>9.90999984741211</v>
+      </c>
+      <c r="F2717" t="n">
         <v>10</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>10.0500001907349</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>10.2600002288818</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>281395</v>
+        <v>527400</v>
       </c>
       <c r="C2718" t="n">
-        <v>10.3400001525879</v>
+        <v>10.2799997329712</v>
       </c>
       <c r="D2718" t="n">
-        <v>9.98999977111816</v>
+        <v>10</v>
       </c>
       <c r="E2718" t="n">
-        <v>10.1499996185303</v>
+        <v>10.0500001907349</v>
       </c>
       <c r="F2718" t="n">
-        <v>10.1700000762939</v>
+        <v>10.2600002288818</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>223525</v>
+        <v>281395</v>
       </c>
       <c r="C2719" t="n">
-        <v>10.1899995803833</v>
+        <v>10.3400001525879</v>
       </c>
       <c r="D2719" t="n">
-        <v>10.0200004577637</v>
+        <v>9.98999977111816</v>
       </c>
       <c r="E2719" t="n">
-        <v>10.0799999237061</v>
+        <v>10.1499996185303</v>
       </c>
       <c r="F2719" t="n">
-        <v>10.0699996948242</v>
+        <v>10.1700000762939</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>221469</v>
+        <v>223525</v>
       </c>
       <c r="C2720" t="n">
-        <v>10.1999998092651</v>
+        <v>10.1899995803833</v>
       </c>
       <c r="D2720" t="n">
-        <v>9.94999980926514</v>
+        <v>10.0200004577637</v>
       </c>
       <c r="E2720" t="n">
-        <v>10.1300001144409</v>
+        <v>10.0799999237061</v>
       </c>
       <c r="F2720" t="n">
-        <v>10.1800003051758</v>
+        <v>10.0699996948242</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>325154</v>
+        <v>221469</v>
       </c>
       <c r="C2721" t="n">
-        <v>10.289999961853</v>
+        <v>10.1999998092651</v>
       </c>
       <c r="D2721" t="n">
-        <v>10.1000003814697</v>
+        <v>9.94999980926514</v>
       </c>
       <c r="E2721" t="n">
+        <v>10.1300001144409</v>
+      </c>
+      <c r="F2721" t="n">
         <v>10.1800003051758</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>10.1499996185303</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>374712</v>
+        <v>325154</v>
       </c>
       <c r="C2722" t="n">
-        <v>10.5299997329712</v>
+        <v>10.289999961853</v>
       </c>
       <c r="D2722" t="n">
-        <v>10.1099996566772</v>
+        <v>10.1000003814697</v>
       </c>
       <c r="E2722" t="n">
-        <v>10.1099996566772</v>
+        <v>10.1800003051758</v>
       </c>
       <c r="F2722" t="n">
-        <v>10.3800001144409</v>
+        <v>10.1499996185303</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>623651</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>10.3100004196167</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>10.1800003051758</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.76094055175781</v>
       </c>
       <c r="G2" t="n">
-        <v>6.97151184082031</v>
+        <v>6.97151041030884</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.72497844696045</v>
       </c>
       <c r="G3" t="n">
-        <v>6.94289493560791</v>
+        <v>6.94289350509644</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.46524620056152</v>
       </c>
       <c r="G4" t="n">
-        <v>6.73621225357056</v>
+        <v>6.7362117767334</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.99373388290405</v>
       </c>
       <c r="G6" t="n">
-        <v>6.36100769042969</v>
+        <v>6.36100721359253</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.06566047668457</v>
       </c>
       <c r="G8" t="n">
-        <v>6.41824340820312</v>
+        <v>6.41824293136597</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.59214878082275</v>
       </c>
       <c r="G11" t="n">
-        <v>6.04144668579102</v>
+        <v>6.04144620895386</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>7.66807079315186</v>
       </c>
       <c r="G13" t="n">
-        <v>6.10186195373535</v>
+        <v>6.10186100006104</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.63610410690308</v>
       </c>
       <c r="G16" t="n">
-        <v>6.07642364501953</v>
+        <v>6.07642412185669</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.70603084564209</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1320686340332</v>
+        <v>6.13206815719604</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>7.72201490402222</v>
       </c>
       <c r="G18" t="n">
-        <v>6.14478731155396</v>
+        <v>6.1447868347168</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.80592823028564</v>
       </c>
       <c r="G19" t="n">
-        <v>6.21156072616577</v>
+        <v>6.21156120300293</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.53620719909668</v>
       </c>
       <c r="G21" t="n">
-        <v>5.99693059921265</v>
+        <v>5.99693012237549</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.40434312820435</v>
       </c>
       <c r="G23" t="n">
-        <v>5.8919997215271</v>
+        <v>5.89200019836426</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.32242822647095</v>
       </c>
       <c r="G24" t="n">
-        <v>5.82681655883789</v>
+        <v>5.82681608200073</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>6.97079181671143</v>
       </c>
       <c r="G26" t="n">
-        <v>5.54700183868408</v>
+        <v>5.54700136184692</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.74102878570557</v>
       </c>
       <c r="G28" t="n">
-        <v>5.3641676902771</v>
+        <v>5.36416864395142</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.9348292350769</v>
       </c>
       <c r="G30" t="n">
-        <v>5.51838493347168</v>
+        <v>5.51838397979736</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.62211799621582</v>
       </c>
       <c r="G37" t="n">
-        <v>6.06529378890991</v>
+        <v>6.06529426574707</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.46827697753906</v>
       </c>
       <c r="G38" t="n">
-        <v>5.94287586212158</v>
+        <v>5.94287538528442</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.30244922637939</v>
       </c>
       <c r="G39" t="n">
-        <v>5.81091737747192</v>
+        <v>5.81091833114624</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.42232513427734</v>
       </c>
       <c r="G40" t="n">
-        <v>5.9063081741333</v>
+        <v>5.90630912780762</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.72800922393799</v>
       </c>
       <c r="G44" t="n">
-        <v>6.1495566368103</v>
+        <v>6.14955759048462</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.65505027770996</v>
       </c>
       <c r="G46" t="n">
-        <v>6.88724946975708</v>
+        <v>6.88724899291992</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.69700717926025</v>
       </c>
       <c r="G47" t="n">
-        <v>6.9206371307373</v>
+        <v>6.92063522338867</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.65105438232422</v>
       </c>
       <c r="G48" t="n">
-        <v>6.88406991958618</v>
+        <v>6.88406944274902</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.701003074646</v>
       </c>
       <c r="G49" t="n">
-        <v>6.92381715774536</v>
+        <v>6.9238166809082</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.64106464385986</v>
       </c>
       <c r="G50" t="n">
-        <v>6.87612009048462</v>
+        <v>6.87611961364746</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.63507080078125</v>
       </c>
       <c r="G51" t="n">
-        <v>6.87135028839111</v>
+        <v>6.87135124206543</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.75095081329346</v>
       </c>
       <c r="G52" t="n">
-        <v>6.96356296539307</v>
+        <v>6.96356248855591</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>8.72897434234619</v>
       </c>
       <c r="G53" t="n">
-        <v>6.94607400894165</v>
+        <v>6.94607496261597</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.85883903503418</v>
       </c>
       <c r="G54" t="n">
-        <v>7.04941511154175</v>
+        <v>7.04941368103027</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.72697639465332</v>
       </c>
       <c r="G55" t="n">
-        <v>6.94448471069336</v>
+        <v>6.9444842338562</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.83486366271973</v>
       </c>
       <c r="G56" t="n">
-        <v>7.03033590316772</v>
+        <v>7.03033494949341</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>8.64705753326416</v>
       </c>
       <c r="G57" t="n">
-        <v>6.88088893890381</v>
+        <v>6.88088846206665</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.88281536102295</v>
       </c>
       <c r="G58" t="n">
-        <v>7.06849384307861</v>
+        <v>7.06849241256714</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.7409610748291</v>
       </c>
       <c r="G59" t="n">
-        <v>6.95561218261719</v>
+        <v>6.95561408996582</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.73896312713623</v>
       </c>
       <c r="G60" t="n">
-        <v>6.95402383804321</v>
+        <v>6.95402240753174</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.76094055175781</v>
       </c>
       <c r="G61" t="n">
-        <v>6.97151184082031</v>
+        <v>6.97151041030884</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93875694274902</v>
       </c>
       <c r="G62" t="n">
-        <v>7.11300945281982</v>
+        <v>7.11300754547119</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.08061027526855</v>
       </c>
       <c r="G63" t="n">
-        <v>7.22588729858398</v>
+        <v>7.22588872909546</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.98870468139648</v>
       </c>
       <c r="G65" t="n">
-        <v>7.15275478363037</v>
+        <v>7.15275382995605</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.73097229003906</v>
       </c>
       <c r="G66" t="n">
-        <v>6.9476637840271</v>
+        <v>6.94766473770142</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.78491592407227</v>
       </c>
       <c r="G67" t="n">
-        <v>6.99059057235718</v>
+        <v>6.99058961868286</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.75294876098633</v>
       </c>
       <c r="G68" t="n">
-        <v>6.96515226364136</v>
+        <v>6.96515083312988</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.88880825042725</v>
       </c>
       <c r="G69" t="n">
-        <v>7.07326221466064</v>
+        <v>7.07326316833496</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.99070262908936</v>
       </c>
       <c r="G71" t="n">
-        <v>7.15434551239014</v>
+        <v>7.15434408187866</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.05064105987549</v>
       </c>
       <c r="G72" t="n">
-        <v>7.20203876495361</v>
+        <v>7.20203971862793</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.03465843200684</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18932199478149</v>
+        <v>7.18932151794434</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.99070262908936</v>
       </c>
       <c r="G75" t="n">
-        <v>7.15434551239014</v>
+        <v>7.15434408187866</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.13055896759033</v>
       </c>
       <c r="G77" t="n">
-        <v>7.26563453674316</v>
+        <v>7.26563501358032</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.17850875854492</v>
       </c>
       <c r="G78" t="n">
-        <v>7.3037896156311</v>
+        <v>7.30379104614258</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.42825126647949</v>
       </c>
       <c r="G80" t="n">
-        <v>7.50252437591553</v>
+        <v>7.50252389907837</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.33035182952881</v>
       </c>
       <c r="G81" t="n">
-        <v>7.42461967468262</v>
+        <v>7.4246187210083</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.38829231262207</v>
       </c>
       <c r="G82" t="n">
-        <v>7.47072410583496</v>
+        <v>7.47072505950928</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.46021842956543</v>
       </c>
       <c r="G83" t="n">
-        <v>7.52796030044556</v>
+        <v>7.52796125411987</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.3723087310791</v>
       </c>
       <c r="G84" t="n">
-        <v>7.45800685882568</v>
+        <v>7.4580078125</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.43624210357666</v>
       </c>
       <c r="G85" t="n">
-        <v>7.50888156890869</v>
+        <v>7.50888109207153</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.3723087310791</v>
       </c>
       <c r="G86" t="n">
-        <v>7.45800685882568</v>
+        <v>7.4580078125</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.38829231262207</v>
       </c>
       <c r="G89" t="n">
-        <v>7.47072410583496</v>
+        <v>7.47072505950928</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.42225742340088</v>
       </c>
       <c r="G90" t="n">
-        <v>7.49775362014771</v>
+        <v>7.49775266647339</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.60007286071777</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63924932479858</v>
+        <v>7.6392502784729</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>10.3592882156372</v>
       </c>
       <c r="G92" t="n">
-        <v>8.24339580535889</v>
+        <v>8.24339389801025</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>10.3892574310303</v>
       </c>
       <c r="G93" t="n">
-        <v>8.26724243164062</v>
+        <v>8.26724338531494</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G94" t="n">
-        <v>8.27519226074219</v>
+        <v>8.2751932144165</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G95" t="n">
-        <v>8.31493949890137</v>
+        <v>8.31493663787842</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>10.2993497848511</v>
       </c>
       <c r="G96" t="n">
-        <v>8.19569969177246</v>
+        <v>8.19569778442383</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>10.2194328308105</v>
       </c>
       <c r="G97" t="n">
-        <v>8.13210582733154</v>
+        <v>8.13210487365723</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G98" t="n">
-        <v>8.12415504455566</v>
+        <v>8.12415599822998</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>10.2793712615967</v>
       </c>
       <c r="G99" t="n">
-        <v>8.17980098724365</v>
+        <v>8.17980003356934</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>10.2494020462036</v>
       </c>
       <c r="G100" t="n">
-        <v>8.2847728729248</v>
+        <v>8.28477478027344</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>10.1694841384888</v>
       </c>
       <c r="G101" t="n">
-        <v>8.22017478942871</v>
+        <v>8.22017574310303</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>10.2494020462036</v>
       </c>
       <c r="G102" t="n">
-        <v>8.2847728729248</v>
+        <v>8.28477478027344</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>10.2394123077393</v>
       </c>
       <c r="G103" t="n">
-        <v>8.27669906616211</v>
+        <v>8.27670001983643</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>10.1794738769531</v>
       </c>
       <c r="G104" t="n">
-        <v>8.22824859619141</v>
+        <v>8.22825050354004</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>10.1894636154175</v>
       </c>
       <c r="G105" t="n">
-        <v>8.23632526397705</v>
+        <v>8.23632621765137</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>10.3592882156372</v>
       </c>
       <c r="G106" t="n">
-        <v>8.37359809875488</v>
+        <v>8.37359619140625</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>10.4991426467896</v>
       </c>
       <c r="G108" t="n">
-        <v>8.48664569854736</v>
+        <v>8.48664474487305</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>10.4991426467896</v>
       </c>
       <c r="G109" t="n">
-        <v>8.48664569854736</v>
+        <v>8.48664474487305</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>10.3592882156372</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37359809875488</v>
+        <v>8.37359619140625</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>10.7788543701172</v>
       </c>
       <c r="G111" t="n">
-        <v>8.71274089813232</v>
+        <v>8.71273994445801</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>10.6689682006836</v>
       </c>
       <c r="G112" t="n">
-        <v>8.62391662597656</v>
+        <v>8.62391757965088</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.7559118270874</v>
       </c>
       <c r="G116" t="n">
-        <v>7.88587713241577</v>
+        <v>7.88587856292725</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G117" t="n">
-        <v>8.07482814788818</v>
+        <v>8.07482719421387</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>10.3492975234985</v>
       </c>
       <c r="G119" t="n">
-        <v>8.36552143096924</v>
+        <v>8.36552238464355</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.4891538619995</v>
       </c>
       <c r="G123" t="n">
-        <v>8.47857093811035</v>
+        <v>8.47856998443604</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.93572616577148</v>
       </c>
       <c r="G124" t="n">
-        <v>8.03122425079346</v>
+        <v>8.03122329711914</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.19249439239502</v>
       </c>
       <c r="G125" t="n">
-        <v>7.43045568466187</v>
+        <v>7.43045711517334</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.92973232269287</v>
       </c>
       <c r="G126" t="n">
-        <v>8.02637958526611</v>
+        <v>8.0263786315918</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.69597434997559</v>
       </c>
       <c r="G127" t="n">
-        <v>7.83742904663086</v>
+        <v>7.83742809295654</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.87179183959961</v>
       </c>
       <c r="G128" t="n">
-        <v>7.9795446395874</v>
+        <v>7.97954511642456</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>10.1694841384888</v>
       </c>
       <c r="G129" t="n">
-        <v>8.22017478942871</v>
+        <v>8.22017574310303</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.90975284576416</v>
       </c>
       <c r="G130" t="n">
-        <v>8.01023006439209</v>
+        <v>8.01022815704346</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.4402379989624</v>
       </c>
       <c r="G131" t="n">
-        <v>7.63071250915527</v>
+        <v>7.63071346282959</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.23844718933105</v>
       </c>
       <c r="G132" t="n">
-        <v>7.46760129928589</v>
+        <v>7.46760034561157</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.23644924163818</v>
       </c>
       <c r="G133" t="n">
-        <v>7.46598720550537</v>
+        <v>7.46598529815674</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.57010364532471</v>
       </c>
       <c r="G134" t="n">
-        <v>7.73568534851074</v>
+        <v>7.73568630218506</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.65801334381104</v>
       </c>
       <c r="G135" t="n">
-        <v>7.80674409866333</v>
+        <v>7.80674362182617</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.68997955322266</v>
       </c>
       <c r="G136" t="n">
-        <v>7.83258247375488</v>
+        <v>7.8325834274292</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.7978687286377</v>
       </c>
       <c r="G138" t="n">
-        <v>7.91979026794434</v>
+        <v>7.91979169845581</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.75990772247314</v>
       </c>
       <c r="G139" t="n">
-        <v>7.88910722732544</v>
+        <v>7.88910579681396</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.90575695037842</v>
       </c>
       <c r="G140" t="n">
-        <v>8.00699996948242</v>
+        <v>8.00700092315674</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.74991798400879</v>
       </c>
       <c r="G141" t="n">
-        <v>7.88103151321411</v>
+        <v>7.88103199005127</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.82583999633789</v>
       </c>
       <c r="G143" t="n">
-        <v>7.94240093231201</v>
+        <v>7.94240140914917</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.0096502304077</v>
       </c>
       <c r="G144" t="n">
-        <v>8.09097862243652</v>
+        <v>8.09097766876221</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G146" t="n">
-        <v>8.17980098724365</v>
+        <v>8.17980194091797</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>10.2294216156006</v>
       </c>
       <c r="G147" t="n">
-        <v>8.26862335205078</v>
+        <v>8.2686243057251</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>10.0595979690552</v>
       </c>
       <c r="G148" t="n">
-        <v>8.1313533782959</v>
+        <v>8.13135147094727</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G149" t="n">
-        <v>8.43819522857666</v>
+        <v>8.43819332122803</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>10.5490922927856</v>
       </c>
       <c r="G150" t="n">
-        <v>8.52702045440674</v>
+        <v>8.52701854705811</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>10.3492975234985</v>
       </c>
       <c r="G151" t="n">
-        <v>8.36552143096924</v>
+        <v>8.36552238464355</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G152" t="n">
-        <v>8.30092334747314</v>
+        <v>8.30092430114746</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31707286834717</v>
+        <v>8.31707191467285</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G154" t="n">
-        <v>8.43819522857666</v>
+        <v>8.43819332122803</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G155" t="n">
-        <v>8.40589618682861</v>
+        <v>8.40589714050293</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G156" t="n">
-        <v>8.49472045898438</v>
+        <v>8.49471950531006</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G157" t="n">
-        <v>8.44626998901367</v>
+        <v>8.44626903533936</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G158" t="n">
-        <v>8.50279426574707</v>
+        <v>8.50279331207275</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.1594953536987</v>
       </c>
       <c r="G162" t="n">
-        <v>8.21210193634033</v>
+        <v>8.21210098266602</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>10.1095457077026</v>
       </c>
       <c r="G164" t="n">
-        <v>8.17172431945801</v>
+        <v>8.17172718048096</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G166" t="n">
-        <v>8.30092334747314</v>
+        <v>8.30092430114746</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G167" t="n">
-        <v>8.40589618682861</v>
+        <v>8.40589714050293</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G168" t="n">
-        <v>8.40589618682861</v>
+        <v>8.40589714050293</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.3492975234985</v>
       </c>
       <c r="G169" t="n">
-        <v>8.36552143096924</v>
+        <v>8.36552238464355</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.4092359542847</v>
       </c>
       <c r="G170" t="n">
-        <v>8.41396999359131</v>
+        <v>8.41397094726562</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G171" t="n">
-        <v>8.454345703125</v>
+        <v>8.45434474945068</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G172" t="n">
-        <v>8.454345703125</v>
+        <v>8.45434474945068</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G174" t="n">
-        <v>8.47049617767334</v>
+        <v>8.47049522399902</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>10.4991426467896</v>
       </c>
       <c r="G175" t="n">
-        <v>8.48664569854736</v>
+        <v>8.48664474487305</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G177" t="n">
-        <v>8.59969139099121</v>
+        <v>8.59969329833984</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.4891538619995</v>
       </c>
       <c r="G178" t="n">
-        <v>8.47857093811035</v>
+        <v>8.47856998443604</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G181" t="n">
-        <v>8.43819522857666</v>
+        <v>8.43819332122803</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.3492975234985</v>
       </c>
       <c r="G185" t="n">
-        <v>8.36552143096924</v>
+        <v>8.36552238464355</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.688946723938</v>
       </c>
       <c r="G187" t="n">
-        <v>8.64006519317627</v>
+        <v>8.64006614685059</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G188" t="n">
-        <v>8.54316902160645</v>
+        <v>8.54316806793213</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G189" t="n">
-        <v>8.55931758880615</v>
+        <v>8.55931663513184</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G190" t="n">
-        <v>8.44626998901367</v>
+        <v>8.44626903533936</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G192" t="n">
-        <v>8.54316902160645</v>
+        <v>8.54316806793213</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G193" t="n">
-        <v>8.57546901702881</v>
+        <v>8.57546710968018</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G194" t="n">
-        <v>8.65621662139893</v>
+        <v>8.65621566772461</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G196" t="n">
-        <v>8.55931758880615</v>
+        <v>8.55931663513184</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>10.5990400314331</v>
       </c>
       <c r="G197" t="n">
-        <v>8.5673942565918</v>
+        <v>8.56739139556885</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G198" t="n">
-        <v>8.55931758880615</v>
+        <v>8.55931663513184</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G199" t="n">
-        <v>8.55931758880615</v>
+        <v>8.55931663513184</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1894636154175</v>
       </c>
       <c r="G202" t="n">
-        <v>8.23632526397705</v>
+        <v>8.23632621765137</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G204" t="n">
-        <v>8.54316902160645</v>
+        <v>8.54316806793213</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G205" t="n">
-        <v>8.49472045898438</v>
+        <v>8.49471950531006</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G206" t="n">
-        <v>8.57546901702881</v>
+        <v>8.57546710968018</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G207" t="n">
-        <v>8.5835428237915</v>
+        <v>8.58354187011719</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.5291118621826</v>
       </c>
       <c r="G208" t="n">
-        <v>8.51086902618408</v>
+        <v>8.51086807250977</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G209" t="n">
-        <v>8.55931758880615</v>
+        <v>8.55931663513184</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.8787508010864</v>
       </c>
       <c r="G211" t="n">
-        <v>8.79348754882812</v>
+        <v>8.79348850250244</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>10.9986267089844</v>
       </c>
       <c r="G212" t="n">
-        <v>8.89038467407227</v>
+        <v>8.89038562774658</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G213" t="n">
-        <v>9.02765846252441</v>
+        <v>9.0276575088501</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>11.2483692169189</v>
       </c>
       <c r="G214" t="n">
-        <v>9.09225749969482</v>
+        <v>9.09225654602051</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>11.258358001709</v>
       </c>
       <c r="G215" t="n">
-        <v>9.10033130645752</v>
+        <v>9.1003303527832</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G216" t="n">
-        <v>8.89846038818359</v>
+        <v>8.89846134185791</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G218" t="n">
-        <v>8.53509521484375</v>
+        <v>8.53509330749512</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G221" t="n">
-        <v>8.92268657684326</v>
+        <v>8.92268562316895</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G222" t="n">
-        <v>8.75311374664307</v>
+        <v>8.75311470031738</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G227" t="n">
-        <v>8.59969139099121</v>
+        <v>8.59969329833984</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G228" t="n">
-        <v>8.5835428237915</v>
+        <v>8.58354187011719</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.6689682006836</v>
       </c>
       <c r="G229" t="n">
-        <v>8.62391662597656</v>
+        <v>8.62391757965088</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G230" t="n">
-        <v>8.68043994903564</v>
+        <v>8.68044090270996</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G231" t="n">
-        <v>8.68043994903564</v>
+        <v>8.68044090270996</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.7788543701172</v>
       </c>
       <c r="G234" t="n">
-        <v>8.71274089813232</v>
+        <v>8.71273994445801</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G235" t="n">
-        <v>8.68043994903564</v>
+        <v>8.68044090270996</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G237" t="n">
-        <v>8.65621662139893</v>
+        <v>8.65621566772461</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.539101600647</v>
       </c>
       <c r="G238" t="n">
-        <v>8.51894283294678</v>
+        <v>8.51894378662109</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G239" t="n">
-        <v>8.53509521484375</v>
+        <v>8.53509330749512</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G241" t="n">
-        <v>8.86616325378418</v>
+        <v>8.86616134643555</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G243" t="n">
-        <v>8.86616325378418</v>
+        <v>8.86616134643555</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G244" t="n">
-        <v>8.75311374664307</v>
+        <v>8.75311470031738</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G245" t="n">
-        <v>8.89846038818359</v>
+        <v>8.89846134185791</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.7688636779785</v>
       </c>
       <c r="G250" t="n">
-        <v>8.70466327667236</v>
+        <v>8.70466423034668</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.9187097549438</v>
       </c>
       <c r="G252" t="n">
-        <v>8.8257884979248</v>
+        <v>8.82578659057617</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>11.0685548782349</v>
       </c>
       <c r="G253" t="n">
-        <v>8.94690895080566</v>
+        <v>8.94690990447998</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G255" t="n">
-        <v>9.10840702056885</v>
+        <v>9.10840606689453</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G256" t="n">
-        <v>9.22952747344971</v>
+        <v>9.22952938079834</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G257" t="n">
-        <v>9.28605175018311</v>
+        <v>9.28605365753174</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G258" t="n">
-        <v>9.68979358673096</v>
+        <v>9.68979263305664</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G259" t="n">
-        <v>9.74631786346436</v>
+        <v>9.74631881713867</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>11.8177795410156</v>
       </c>
       <c r="G260" t="n">
-        <v>9.55252265930176</v>
+        <v>9.55252170562744</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>11.9576349258423</v>
       </c>
       <c r="G261" t="n">
-        <v>9.66556835174561</v>
+        <v>9.66557025909424</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G264" t="n">
-        <v>9.77861785888672</v>
+        <v>9.77861881256104</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>12.277304649353</v>
       </c>
       <c r="G265" t="n">
-        <v>9.92396545410156</v>
+        <v>9.92396259307861</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G266" t="n">
-        <v>9.74631786346436</v>
+        <v>9.74631881713867</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.3072738647461</v>
       </c>
       <c r="G267" t="n">
-        <v>9.94818878173828</v>
+        <v>9.94818687438965</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G268" t="n">
-        <v>9.93203926086426</v>
+        <v>9.93203830718994</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G269" t="n">
-        <v>9.91588878631592</v>
+        <v>9.9158878326416</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G270" t="n">
-        <v>9.87551689147949</v>
+        <v>9.87551593780518</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G271" t="n">
-        <v>9.93203926086426</v>
+        <v>9.93203830718994</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.1774082183838</v>
       </c>
       <c r="G272" t="n">
-        <v>9.84321594238281</v>
+        <v>9.84321689605713</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G273" t="n">
-        <v>9.89974021911621</v>
+        <v>9.89973926544189</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G274" t="n">
-        <v>9.86744117736816</v>
+        <v>9.86744213104248</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.2972841262817</v>
       </c>
       <c r="G275" t="n">
-        <v>9.94011306762695</v>
+        <v>9.94011211395264</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G277" t="n">
-        <v>9.81899166107178</v>
+        <v>9.81899070739746</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G278" t="n">
-        <v>9.68979358673096</v>
+        <v>9.68979263305664</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11.8477487564087</v>
       </c>
       <c r="G279" t="n">
-        <v>9.57674598693848</v>
+        <v>9.57674694061279</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G280" t="n">
-        <v>9.87551689147949</v>
+        <v>9.87551593780518</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G281" t="n">
-        <v>9.93203926086426</v>
+        <v>9.93203830718994</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G282" t="n">
-        <v>10.0289373397827</v>
+        <v>10.0289363861084</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G285" t="n">
-        <v>9.89974021911621</v>
+        <v>9.89973926544189</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G286" t="n">
-        <v>9.89974021911621</v>
+        <v>9.89973926544189</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G287" t="n">
-        <v>10.0289373397827</v>
+        <v>10.0289363861084</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G288" t="n">
-        <v>10.2388820648193</v>
+        <v>10.238881111145</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G290" t="n">
-        <v>10.230806350708</v>
+        <v>10.2308082580566</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>12.4970779418945</v>
       </c>
       <c r="G292" t="n">
-        <v>10.1016101837158</v>
+        <v>10.1016120910645</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>12.8567056655884</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3923025131226</v>
+        <v>10.3923053741455</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G296" t="n">
-        <v>10.3600044250488</v>
+        <v>10.3600034713745</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>12.5170574188232</v>
       </c>
       <c r="G297" t="n">
-        <v>10.1177597045898</v>
+        <v>10.1177625656128</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G298" t="n">
-        <v>10.3519296646118</v>
+        <v>10.3519287109375</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G299" t="n">
-        <v>10.2388820648193</v>
+        <v>10.238881111145</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G300" t="n">
-        <v>10.4972772598267</v>
+        <v>10.4972763061523</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G301" t="n">
-        <v>10.6587734222412</v>
+        <v>10.6587753295898</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>13.1464061737061</v>
       </c>
       <c r="G302" t="n">
-        <v>10.6264734268188</v>
+        <v>10.6264743804932</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.9566020965576</v>
       </c>
       <c r="G303" t="n">
-        <v>10.4730529785156</v>
+        <v>10.473051071167</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G304" t="n">
-        <v>10.481125831604</v>
+        <v>10.4811267852783</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>13.0764780044556</v>
       </c>
       <c r="G305" t="n">
-        <v>10.5699491500854</v>
+        <v>10.5699510574341</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G306" t="n">
-        <v>10.4892015457153</v>
+        <v>10.489200592041</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G307" t="n">
-        <v>10.4892015457153</v>
+        <v>10.489200592041</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G308" t="n">
-        <v>10.6587734222412</v>
+        <v>10.6587753295898</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G309" t="n">
-        <v>10.7314462661743</v>
+        <v>10.7314472198486</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>13.1064472198486</v>
       </c>
       <c r="G310" t="n">
-        <v>10.5941743850708</v>
+        <v>10.5941753387451</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>13.5060338973999</v>
       </c>
       <c r="G314" t="n">
-        <v>10.9171676635742</v>
+        <v>10.9171686172485</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>13.5759620666504</v>
       </c>
       <c r="G316" t="n">
-        <v>10.9736919403076</v>
+        <v>10.9736909866333</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G317" t="n">
-        <v>11.0302152633667</v>
+        <v>11.030216217041</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>13.7058277130127</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0786657333374</v>
+        <v>11.0786647796631</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>14.1453733444214</v>
       </c>
       <c r="G324" t="n">
-        <v>11.4339580535889</v>
+        <v>11.4339570999146</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.0654563903809</v>
       </c>
       <c r="G327" t="n">
-        <v>11.3693599700928</v>
+        <v>11.3693590164185</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.0554656982422</v>
       </c>
       <c r="G328" t="n">
-        <v>11.3612823486328</v>
+        <v>11.3612833023071</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G330" t="n">
-        <v>11.4420318603516</v>
+        <v>11.4420328140259</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.9455795288086</v>
       </c>
       <c r="G333" t="n">
-        <v>11.2724609375</v>
+        <v>11.2724590301514</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.8856420516968</v>
       </c>
       <c r="G335" t="n">
-        <v>11.2240114212036</v>
+        <v>11.2240123748779</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>14.5050010681152</v>
       </c>
       <c r="G337" t="n">
-        <v>11.7246513366699</v>
+        <v>11.7246503829956</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>14.3351774215698</v>
       </c>
       <c r="G338" t="n">
-        <v>11.5873785018921</v>
+        <v>11.5873794555664</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G339" t="n">
-        <v>11.6600522994995</v>
+        <v>11.6600532531738</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>14.4150943756104</v>
       </c>
       <c r="G340" t="n">
-        <v>11.6519765853882</v>
+        <v>11.6519775390625</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>14.6148881912231</v>
       </c>
       <c r="G341" t="n">
-        <v>11.8134746551514</v>
+        <v>11.8134737014771</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>14.4950122833252</v>
       </c>
       <c r="G342" t="n">
-        <v>11.7165775299072</v>
+        <v>11.7165765762329</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>14.8146810531616</v>
       </c>
       <c r="G345" t="n">
-        <v>11.9749708175659</v>
+        <v>11.9749698638916</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.0444440841675</v>
       </c>
       <c r="G346" t="n">
-        <v>12.1606931686401</v>
+        <v>12.1606922149658</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.0844020843506</v>
       </c>
       <c r="G347" t="n">
-        <v>12.1929903030396</v>
+        <v>12.1929912567139</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.7647333145142</v>
       </c>
       <c r="G348" t="n">
-        <v>11.9345970153809</v>
+        <v>11.9345951080322</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.6648359298706</v>
       </c>
       <c r="G349" t="n">
-        <v>11.8538475036621</v>
+        <v>11.8538465499878</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.5349702835083</v>
       </c>
       <c r="G351" t="n">
-        <v>11.7488746643066</v>
+        <v>11.748875617981</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14.2053108215332</v>
       </c>
       <c r="G354" t="n">
-        <v>11.4824056625366</v>
+        <v>11.4824047088623</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G355" t="n">
-        <v>11.6052560806274</v>
+        <v>11.6052570343018</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G356" t="n">
-        <v>11.6216373443604</v>
+        <v>11.6216354370117</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G357" t="n">
-        <v>11.6216373443604</v>
+        <v>11.6216354370117</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G358" t="n">
-        <v>11.6216373443604</v>
+        <v>11.6216354370117</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G359" t="n">
-        <v>11.6216373443604</v>
+        <v>11.6216354370117</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G360" t="n">
-        <v>11.7281055450439</v>
+        <v>11.7281074523926</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G361" t="n">
-        <v>11.8263854980469</v>
+        <v>11.8263864517212</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G362" t="n">
-        <v>11.6052560806274</v>
+        <v>11.6052570343018</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.9755487442017</v>
       </c>
       <c r="G363" t="n">
-        <v>11.457836151123</v>
+        <v>11.4578351974487</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G365" t="n">
-        <v>11.4824056625366</v>
+        <v>11.4824066162109</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>13.7557764053345</v>
       </c>
       <c r="G367" t="n">
-        <v>11.2776556015015</v>
+        <v>11.2776565551758</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G371" t="n">
-        <v>10.8845357894897</v>
+        <v>10.8845348358154</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>13.0864677429199</v>
       </c>
       <c r="G372" t="n">
-        <v>10.7289247512817</v>
+        <v>10.7289228439331</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.996561050415</v>
       </c>
       <c r="G373" t="n">
-        <v>10.6552124023438</v>
+        <v>10.6552143096924</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G375" t="n">
-        <v>11.1056642532349</v>
+        <v>11.1056632995605</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.386157989502</v>
       </c>
       <c r="G377" t="n">
-        <v>10.9746246337891</v>
+        <v>10.9746236801147</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G378" t="n">
-        <v>10.8599634170532</v>
+        <v>10.8599643707275</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>12.9566020965576</v>
       </c>
       <c r="G379" t="n">
-        <v>10.6224536895752</v>
+        <v>10.6224527359009</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.0764780044556</v>
       </c>
       <c r="G380" t="n">
-        <v>10.7207336425781</v>
+        <v>10.7207345962524</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G382" t="n">
-        <v>10.6470241546631</v>
+        <v>10.6470232009888</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.547025680542</v>
       </c>
       <c r="G383" t="n">
-        <v>10.2866630554199</v>
+        <v>10.2866640090942</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12.7568092346191</v>
       </c>
       <c r="G387" t="n">
-        <v>10.4586524963379</v>
+        <v>10.4586534500122</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.5559825897217</v>
       </c>
       <c r="G389" t="n">
-        <v>11.1138553619385</v>
+        <v>11.1138544082642</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>13.3961477279663</v>
       </c>
       <c r="G391" t="n">
-        <v>10.9828147888184</v>
+        <v>10.982813835144</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>13.8057241439819</v>
       </c>
       <c r="G392" t="n">
-        <v>11.3186044692993</v>
+        <v>11.3186054229736</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.7557764053345</v>
       </c>
       <c r="G393" t="n">
-        <v>11.2776556015015</v>
+        <v>11.2776565551758</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G394" t="n">
-        <v>11.1056642532349</v>
+        <v>11.1056632995605</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.5959405899048</v>
       </c>
       <c r="G395" t="n">
-        <v>11.1466131210327</v>
+        <v>11.146614074707</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G396" t="n">
-        <v>11.0974750518799</v>
+        <v>11.0974740982056</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.5559825897217</v>
       </c>
       <c r="G398" t="n">
-        <v>11.1138553619385</v>
+        <v>11.1138544082642</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G399" t="n">
-        <v>10.8599634170532</v>
+        <v>10.8599643707275</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.2962512969971</v>
       </c>
       <c r="G401" t="n">
-        <v>10.9009132385254</v>
+        <v>10.900915145874</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G403" t="n">
-        <v>10.8599634170532</v>
+        <v>10.8599643707275</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0465087890625</v>
       </c>
       <c r="G404" t="n">
-        <v>10.6961631774902</v>
+        <v>10.6961641311646</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G405" t="n">
-        <v>10.6470241546631</v>
+        <v>10.6470232009888</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G407" t="n">
-        <v>10.7043542861938</v>
+        <v>10.7043533325195</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G409" t="n">
-        <v>10.6470241546631</v>
+        <v>10.6470232009888</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G410" t="n">
-        <v>10.6306428909302</v>
+        <v>10.6306438446045</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G411" t="n">
-        <v>10.5733137130737</v>
+        <v>10.5733118057251</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G412" t="n">
-        <v>10.6470241546631</v>
+        <v>10.6470232009888</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>12.9066543579102</v>
       </c>
       <c r="G413" t="n">
-        <v>10.5815048217773</v>
+        <v>10.581503868103</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G415" t="n">
-        <v>10.4832248687744</v>
+        <v>10.4832239151001</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>12.7568092346191</v>
       </c>
       <c r="G417" t="n">
-        <v>10.4586524963379</v>
+        <v>10.4586534500122</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G419" t="n">
-        <v>10.4095125198364</v>
+        <v>10.4095134735107</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>12.9466133117676</v>
       </c>
       <c r="G421" t="n">
-        <v>10.6142644882202</v>
+        <v>10.6142635345459</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G425" t="n">
-        <v>10.5733137130737</v>
+        <v>10.5733118057251</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>13.1064472198486</v>
       </c>
       <c r="G426" t="n">
-        <v>10.7453031539917</v>
+        <v>10.7453050613403</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.0864677429199</v>
       </c>
       <c r="G427" t="n">
-        <v>10.7289247512817</v>
+        <v>10.7289228439331</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.3461999893188</v>
       </c>
       <c r="G428" t="n">
-        <v>10.9418630599976</v>
+        <v>10.9418659210205</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>13.4960451126099</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0647144317627</v>
+        <v>11.064715385437</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.5160236358643</v>
       </c>
       <c r="G432" t="n">
-        <v>11.0810947418213</v>
+        <v>11.081093788147</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.3961477279663</v>
       </c>
       <c r="G433" t="n">
-        <v>10.9828147888184</v>
+        <v>10.982813835144</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G434" t="n">
-        <v>11.1875648498535</v>
+        <v>11.1875658035278</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>13.5160236358643</v>
       </c>
       <c r="G435" t="n">
-        <v>11.0810947418213</v>
+        <v>11.081093788147</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.5260143280029</v>
       </c>
       <c r="G436" t="n">
-        <v>11.0892858505249</v>
+        <v>11.0892848968506</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.7058277130127</v>
       </c>
       <c r="G438" t="n">
-        <v>11.236704826355</v>
+        <v>11.2367057800293</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G440" t="n">
-        <v>11.6052560806274</v>
+        <v>11.6052570343018</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G442" t="n">
-        <v>11.5888757705688</v>
+        <v>11.5888748168945</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G443" t="n">
-        <v>11.5888757705688</v>
+        <v>11.5888748168945</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>14.0954246520996</v>
       </c>
       <c r="G444" t="n">
-        <v>11.556116104126</v>
+        <v>11.5561151504517</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G445" t="n">
-        <v>11.5888757705688</v>
+        <v>11.5888748168945</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.1653528213501</v>
       </c>
       <c r="G446" t="n">
-        <v>11.6134443283081</v>
+        <v>11.6134462356567</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.2952184677124</v>
       </c>
       <c r="G447" t="n">
-        <v>11.719916343689</v>
+        <v>11.7199172973633</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G448" t="n">
-        <v>11.7281055450439</v>
+        <v>11.7281074523926</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G449" t="n">
-        <v>11.7281055450439</v>
+        <v>11.7281074523926</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G451" t="n">
-        <v>11.7281055450439</v>
+        <v>11.7281074523926</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>14.4150943756104</v>
       </c>
       <c r="G452" t="n">
-        <v>11.8181962966919</v>
+        <v>11.8181972503662</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>14.2752389907837</v>
       </c>
       <c r="G453" t="n">
-        <v>11.7035350799561</v>
+        <v>11.7035360336304</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>14.285228729248</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7117252349854</v>
+        <v>11.7117261886597</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>14.4450626373291</v>
       </c>
       <c r="G456" t="n">
-        <v>11.8427677154541</v>
+        <v>11.8427658081055</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>14.4350738525391</v>
       </c>
       <c r="G457" t="n">
-        <v>11.8345756530762</v>
+        <v>11.8345766067505</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>14.4450626373291</v>
       </c>
       <c r="G458" t="n">
-        <v>11.8427677154541</v>
+        <v>11.8427658081055</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>14.6048984527588</v>
       </c>
       <c r="G459" t="n">
-        <v>11.9738082885742</v>
+        <v>11.9738073348999</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>14.6148881912231</v>
       </c>
       <c r="G460" t="n">
-        <v>11.9819974899292</v>
+        <v>11.9819965362549</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>14.674825668335</v>
       </c>
       <c r="G461" t="n">
-        <v>12.0311365127563</v>
+        <v>12.031135559082</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>14.5749292373657</v>
       </c>
       <c r="G463" t="n">
-        <v>11.949236869812</v>
+        <v>11.9492378234863</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>14.0155067443848</v>
       </c>
       <c r="G469" t="n">
-        <v>11.4905939102173</v>
+        <v>11.4905948638916</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>14.1653528213501</v>
       </c>
       <c r="G470" t="n">
-        <v>11.6134443283081</v>
+        <v>11.6134462356567</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>14.2452697753906</v>
       </c>
       <c r="G471" t="n">
-        <v>11.6789646148682</v>
+        <v>11.6789655685425</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>14.1953220367432</v>
       </c>
       <c r="G473" t="n">
-        <v>11.6380157470703</v>
+        <v>11.6380167007446</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>14.0155067443848</v>
       </c>
       <c r="G475" t="n">
-        <v>11.4905939102173</v>
+        <v>11.4905948638916</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G476" t="n">
-        <v>11.1875648498535</v>
+        <v>11.1875658035278</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.416127204895</v>
       </c>
       <c r="G477" t="n">
-        <v>10.9991941452026</v>
+        <v>10.999195098877</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G478" t="n">
-        <v>10.6470241546631</v>
+        <v>10.6470232009888</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G479" t="n">
-        <v>10.4832248687744</v>
+        <v>10.4832239151001</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G480" t="n">
-        <v>10.5159845352173</v>
+        <v>10.5159826278687</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>12.6868810653687</v>
       </c>
       <c r="G481" t="n">
-        <v>10.4013242721558</v>
+        <v>10.4013233184814</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G485" t="n">
-        <v>10.7043542861938</v>
+        <v>10.7043533325195</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>13.0465087890625</v>
       </c>
       <c r="G487" t="n">
-        <v>10.6961631774902</v>
+        <v>10.6961641311646</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G488" t="n">
-        <v>10.5733137130737</v>
+        <v>10.5733118057251</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>12.8367261886597</v>
       </c>
       <c r="G489" t="n">
-        <v>10.5241737365723</v>
+        <v>10.5241718292236</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G491" t="n">
-        <v>10.7043542861938</v>
+        <v>10.7043533325195</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G492" t="n">
-        <v>10.6388339996338</v>
+        <v>10.6388320922852</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>12.7767877578735</v>
       </c>
       <c r="G493" t="n">
-        <v>10.4750337600708</v>
+        <v>10.4750328063965</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G494" t="n">
-        <v>10.6470241546631</v>
+        <v>10.6470232009888</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G495" t="n">
-        <v>10.4996042251587</v>
+        <v>10.4996023178101</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G499" t="n">
-        <v>10.4095125198364</v>
+        <v>10.4095134735107</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>12.5869846343994</v>
       </c>
       <c r="G503" t="n">
-        <v>10.3194227218628</v>
+        <v>10.3194236755371</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>12.6768922805786</v>
       </c>
       <c r="G505" t="n">
-        <v>10.3931341171265</v>
+        <v>10.3931331634521</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G506" t="n">
-        <v>10.4832248687744</v>
+        <v>10.4832239151001</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G507" t="n">
-        <v>10.4996042251587</v>
+        <v>10.4996023178101</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>12.4171600341797</v>
       </c>
       <c r="G512" t="n">
-        <v>10.180193901062</v>
+        <v>10.1801910400391</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G514" t="n">
-        <v>10.5159845352173</v>
+        <v>10.5159826278687</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>13.1563959121704</v>
       </c>
       <c r="G515" t="n">
-        <v>10.7862548828125</v>
+        <v>10.7862539291382</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G517" t="n">
-        <v>10.8599634170532</v>
+        <v>10.8599643707275</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>13.2063436508179</v>
       </c>
       <c r="G518" t="n">
-        <v>10.8272047042847</v>
+        <v>10.827202796936</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G525" t="n">
-        <v>11.0974750518799</v>
+        <v>11.0974740982056</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G527" t="n">
-        <v>11.1056642532349</v>
+        <v>11.1056632995605</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G529" t="n">
-        <v>10.8845357894897</v>
+        <v>10.8845348358154</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G533" t="n">
-        <v>10.6470241546631</v>
+        <v>10.6470232009888</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G536" t="n">
-        <v>10.4095125198364</v>
+        <v>10.4095134735107</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>12.0875005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>9.90992164611816</v>
+        <v>9.90992259979248</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>12.0475416183472</v>
       </c>
       <c r="G543" t="n">
-        <v>9.87716102600098</v>
+        <v>9.87716197967529</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G544" t="n">
-        <v>9.94268226623535</v>
+        <v>9.94268131256104</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>12.0875005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>9.90992164611816</v>
+        <v>9.90992259979248</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G547" t="n">
-        <v>9.82802200317383</v>
+        <v>9.82802104949951</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>11.7778205871582</v>
       </c>
       <c r="G549" t="n">
-        <v>9.65603160858154</v>
+        <v>9.65603065490723</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.8677282333374</v>
       </c>
       <c r="G551" t="n">
-        <v>9.7297420501709</v>
+        <v>9.72974300384521</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.5280790328979</v>
       </c>
       <c r="G552" t="n">
-        <v>9.45127964019775</v>
+        <v>9.45128059387207</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G553" t="n">
-        <v>9.4185209274292</v>
+        <v>9.41852188110352</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>11.2483692169189</v>
       </c>
       <c r="G554" t="n">
-        <v>9.22196197509766</v>
+        <v>9.22196102142334</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>11.1185026168823</v>
       </c>
       <c r="G555" t="n">
-        <v>9.11548900604248</v>
+        <v>9.1154899597168</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0245838165283</v>
+        <v>10.0245819091797</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G558" t="n">
-        <v>10.3030424118042</v>
+        <v>10.3030433654785</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G560" t="n">
-        <v>10.5159845352173</v>
+        <v>10.5159826278687</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>12.7767877578735</v>
       </c>
       <c r="G561" t="n">
-        <v>10.4750337600708</v>
+        <v>10.4750328063965</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G562" t="n">
-        <v>10.5159845352173</v>
+        <v>10.5159826278687</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>12.9066543579102</v>
       </c>
       <c r="G564" t="n">
-        <v>10.5815048217773</v>
+        <v>10.581503868103</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>12.7068605422974</v>
       </c>
       <c r="G566" t="n">
-        <v>10.4177026748657</v>
+        <v>10.41770362854</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G570" t="n">
-        <v>10.0737209320068</v>
+        <v>10.0737228393555</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>12.3372430801392</v>
       </c>
       <c r="G573" t="n">
-        <v>10.114673614502</v>
+        <v>10.1146726608276</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>12.5270471572876</v>
       </c>
       <c r="G574" t="n">
-        <v>10.2702827453613</v>
+        <v>10.2702836990356</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>12.5070667266846</v>
       </c>
       <c r="G575" t="n">
-        <v>10.2539024353027</v>
+        <v>10.2539033889771</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G576" t="n">
-        <v>10.0573425292969</v>
+        <v>10.0573415756226</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>12.3871908187866</v>
       </c>
       <c r="G577" t="n">
-        <v>10.1556224822998</v>
+        <v>10.1556205749512</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>12.3472318649292</v>
       </c>
       <c r="G578" t="n">
-        <v>10.1228618621826</v>
+        <v>10.1228628158569</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>12.3572216033936</v>
       </c>
       <c r="G579" t="n">
-        <v>10.1310520172119</v>
+        <v>10.1310510635376</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>12.3772010803223</v>
       </c>
       <c r="G580" t="n">
-        <v>10.1474332809448</v>
+        <v>10.1474323272705</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G582" t="n">
-        <v>10.0737209320068</v>
+        <v>10.0737228393555</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G583" t="n">
-        <v>10.0737209320068</v>
+        <v>10.0737228393555</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G584" t="n">
-        <v>10.0573425292969</v>
+        <v>10.0573415756226</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>12.1374492645264</v>
       </c>
       <c r="G587" t="n">
-        <v>9.95087146759033</v>
+        <v>9.95087242126465</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G589" t="n">
-        <v>9.94268226623535</v>
+        <v>9.94268131256104</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G590" t="n">
-        <v>10.0082025527954</v>
+        <v>10.0082035064697</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>12.0375528335571</v>
       </c>
       <c r="G591" t="n">
-        <v>9.868971824646</v>
+        <v>9.86897277832031</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G593" t="n">
-        <v>9.94268226623535</v>
+        <v>9.94268131256104</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G596" t="n">
-        <v>10.4996042251587</v>
+        <v>10.4996023178101</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G597" t="n">
-        <v>10.6306428909302</v>
+        <v>10.6306438446045</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>12.4970779418945</v>
       </c>
       <c r="G600" t="n">
-        <v>10.2457132339478</v>
+        <v>10.2457141876221</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G603" t="n">
-        <v>9.99182319641113</v>
+        <v>9.99182224273682</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>12.1074800491333</v>
       </c>
       <c r="G604" t="n">
-        <v>9.92630195617676</v>
+        <v>9.92630290985107</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>11.7878112792969</v>
       </c>
       <c r="G607" t="n">
-        <v>9.66422271728516</v>
+        <v>9.66422176361084</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>11.6979036331177</v>
       </c>
       <c r="G608" t="n">
-        <v>9.77271461486816</v>
+        <v>9.77271556854248</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>12.5370359420776</v>
       </c>
       <c r="G611" t="n">
-        <v>10.4737462997437</v>
+        <v>10.4737453460693</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>12.427149772644</v>
       </c>
       <c r="G612" t="n">
-        <v>10.3819456100464</v>
+        <v>10.3819437026978</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>11.9076871871948</v>
       </c>
       <c r="G614" t="n">
-        <v>9.94797229766846</v>
+        <v>9.94797325134277</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G616" t="n">
-        <v>10.2150325775146</v>
+        <v>10.2150316238403</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>12.3871908187866</v>
       </c>
       <c r="G617" t="n">
-        <v>10.3485622406006</v>
+        <v>10.3485612869263</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>12.4371385574341</v>
       </c>
       <c r="G618" t="n">
-        <v>10.3902902603149</v>
+        <v>10.3902893066406</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G619" t="n">
-        <v>10.3652534484863</v>
+        <v>10.3652544021606</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>12.4671087265015</v>
       </c>
       <c r="G620" t="n">
-        <v>10.4153280258179</v>
+        <v>10.4153270721436</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G621" t="n">
-        <v>10.6323127746582</v>
+        <v>10.6323137283325</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>12.427149772644</v>
       </c>
       <c r="G623" t="n">
-        <v>10.3819456100464</v>
+        <v>10.3819437026978</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G628" t="n">
-        <v>10.2150325775146</v>
+        <v>10.2150316238403</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G629" t="n">
-        <v>10.1065397262573</v>
+        <v>10.1065406799316</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>11.7978010177612</v>
       </c>
       <c r="G632" t="n">
-        <v>9.85617160797119</v>
+        <v>9.85617256164551</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G634" t="n">
-        <v>9.79775142669678</v>
+        <v>9.79775238037109</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>11.7078943252563</v>
       </c>
       <c r="G635" t="n">
-        <v>9.78106117248535</v>
+        <v>9.78106021881104</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>11.5780277252197</v>
       </c>
       <c r="G637" t="n">
-        <v>9.67256641387939</v>
+        <v>9.67256736755371</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>11.3382759094238</v>
       </c>
       <c r="G638" t="n">
-        <v>9.4722728729248</v>
+        <v>9.47227191925049</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>11.4981098175049</v>
       </c>
       <c r="G642" t="n">
-        <v>9.60580253601074</v>
+        <v>9.60580158233643</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>11.6279764175415</v>
       </c>
       <c r="G643" t="n">
-        <v>9.71429538726807</v>
+        <v>9.71429634094238</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>11.9376564025879</v>
       </c>
       <c r="G644" t="n">
-        <v>9.9730110168457</v>
+        <v>9.97301006317139</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G645" t="n">
-        <v>9.79775142669678</v>
+        <v>9.79775238037109</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>11.9776153564453</v>
       </c>
       <c r="G646" t="n">
-        <v>10.0063934326172</v>
+        <v>10.0063915252686</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.9076871871948</v>
       </c>
       <c r="G648" t="n">
-        <v>9.94797229766846</v>
+        <v>9.94797325134277</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G652" t="n">
-        <v>10.148265838623</v>
+        <v>10.1482667922974</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G653" t="n">
-        <v>10.1065397262573</v>
+        <v>10.1065406799316</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G654" t="n">
-        <v>10.2150325775146</v>
+        <v>10.2150316238403</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>11.7078943252563</v>
       </c>
       <c r="G659" t="n">
-        <v>9.78106117248535</v>
+        <v>9.78106021881104</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.6779251098633</v>
       </c>
       <c r="G660" t="n">
-        <v>9.75602340698242</v>
+        <v>9.75602436065674</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G662" t="n">
-        <v>9.76436901092529</v>
+        <v>9.76436805725098</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G666" t="n">
-        <v>9.79775142669678</v>
+        <v>9.79775238037109</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.3882236480713</v>
       </c>
       <c r="G667" t="n">
-        <v>9.51399993896484</v>
+        <v>9.51400089263916</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.2983169555664</v>
       </c>
       <c r="G668" t="n">
-        <v>9.438889503479</v>
+        <v>9.43889045715332</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.3782339096069</v>
       </c>
       <c r="G669" t="n">
-        <v>9.50565433502197</v>
+        <v>9.50565528869629</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G670" t="n">
-        <v>9.41385269165039</v>
+        <v>9.41385173797607</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.128493309021</v>
       </c>
       <c r="G671" t="n">
-        <v>9.29701614379883</v>
+        <v>9.29701519012451</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G672" t="n">
-        <v>9.330397605896</v>
+        <v>9.33039665222168</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.0285959243774</v>
       </c>
       <c r="G674" t="n">
-        <v>9.21355819702148</v>
+        <v>9.21355724334717</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G676" t="n">
-        <v>9.330397605896</v>
+        <v>9.33039665222168</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.2084102630615</v>
       </c>
       <c r="G677" t="n">
-        <v>9.36378002166748</v>
+        <v>9.3637809753418</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G678" t="n">
-        <v>9.330397605896</v>
+        <v>9.33039665222168</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>11.7978010177612</v>
       </c>
       <c r="G680" t="n">
-        <v>9.85617160797119</v>
+        <v>9.85617256164551</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>11.4981098175049</v>
       </c>
       <c r="G682" t="n">
-        <v>9.60580253601074</v>
+        <v>9.60580158233643</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.3582553863525</v>
       </c>
       <c r="G683" t="n">
-        <v>9.48896408081055</v>
+        <v>9.48896598815918</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.1484718322754</v>
       </c>
       <c r="G685" t="n">
-        <v>9.31370544433594</v>
+        <v>9.31370449066162</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.3282861709595</v>
       </c>
       <c r="G687" t="n">
-        <v>9.46392631530762</v>
+        <v>9.46392726898193</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.1884307861328</v>
       </c>
       <c r="G688" t="n">
-        <v>9.34708786010742</v>
+        <v>9.34708881378174</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>11.6279764175415</v>
       </c>
       <c r="G692" t="n">
-        <v>9.71429538726807</v>
+        <v>9.71429634094238</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G693" t="n">
-        <v>9.76436901092529</v>
+        <v>9.76436805725098</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>11.8577394485474</v>
       </c>
       <c r="G694" t="n">
-        <v>9.90624523162842</v>
+        <v>9.9062442779541</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>11.9376564025879</v>
       </c>
       <c r="G695" t="n">
-        <v>9.9730110168457</v>
+        <v>9.97301006317139</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>11.8976974487305</v>
       </c>
       <c r="G696" t="n">
-        <v>9.93962669372559</v>
+        <v>9.9396276473999</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G697" t="n">
-        <v>9.79775142669678</v>
+        <v>9.79775238037109</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G701" t="n">
-        <v>9.41385269165039</v>
+        <v>9.41385173797607</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>11.0885343551636</v>
       </c>
       <c r="G705" t="n">
-        <v>9.26363277435303</v>
+        <v>9.26363372802734</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>11.1484718322754</v>
       </c>
       <c r="G706" t="n">
-        <v>9.31370544433594</v>
+        <v>9.31370449066162</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G707" t="n">
-        <v>8.96318912506104</v>
+        <v>8.96319007873535</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G709" t="n">
-        <v>8.4541072845459</v>
+        <v>8.45410823822021</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.92473697662354</v>
       </c>
       <c r="G710" t="n">
-        <v>8.29136753082275</v>
+        <v>8.29136848449707</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>9.8248405456543</v>
       </c>
       <c r="G711" t="n">
-        <v>8.20791053771973</v>
+        <v>8.20791149139404</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>9.45522308349609</v>
       </c>
       <c r="G712" t="n">
-        <v>7.89912462234497</v>
+        <v>7.89912509918213</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>9.9197416305542</v>
       </c>
       <c r="G714" t="n">
-        <v>8.28719425201416</v>
+        <v>8.28719329833984</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.66001129150391</v>
       </c>
       <c r="G716" t="n">
-        <v>8.07021141052246</v>
+        <v>8.07020950317383</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.50517082214355</v>
       </c>
       <c r="G717" t="n">
-        <v>7.94085264205933</v>
+        <v>7.9408540725708</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.41026878356934</v>
       </c>
       <c r="G719" t="n">
-        <v>7.86156940460205</v>
+        <v>7.86156845092773</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.72494411468506</v>
       </c>
       <c r="G720" t="n">
-        <v>8.12445545196533</v>
+        <v>8.12445640563965</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.57509899139404</v>
       </c>
       <c r="G721" t="n">
-        <v>7.99927091598511</v>
+        <v>7.99927234649658</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.8248405456543</v>
       </c>
       <c r="G723" t="n">
-        <v>8.20791053771973</v>
+        <v>8.20791149139404</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G726" t="n">
-        <v>8.4541072845459</v>
+        <v>8.45410823822021</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>9.88477897644043</v>
       </c>
       <c r="G727" t="n">
-        <v>8.25798606872559</v>
+        <v>8.2579870223999</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>9.83483028411865</v>
       </c>
       <c r="G728" t="n">
-        <v>8.21625804901123</v>
+        <v>8.2162561416626</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>9.5850887298584</v>
       </c>
       <c r="G729" t="n">
-        <v>8.00761699676514</v>
+        <v>8.00761890411377</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>9.44523334503174</v>
       </c>
       <c r="G730" t="n">
-        <v>7.89077806472778</v>
+        <v>7.8907790184021</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>9.07061958312988</v>
       </c>
       <c r="G732" t="n">
-        <v>7.57781744003296</v>
+        <v>7.57781648635864</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>8.99569797515869</v>
       </c>
       <c r="G733" t="n">
-        <v>7.51522588729858</v>
+        <v>7.51522541046143</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>9.04564571380615</v>
       </c>
       <c r="G734" t="n">
-        <v>7.55695390701294</v>
+        <v>7.55695295333862</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>9.11557388305664</v>
       </c>
       <c r="G735" t="n">
-        <v>7.6153736114502</v>
+        <v>7.61537265777588</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.31536674499512</v>
       </c>
       <c r="G736" t="n">
-        <v>7.78228521347046</v>
+        <v>7.7822847366333</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.34533596038818</v>
       </c>
       <c r="G737" t="n">
-        <v>7.80732202529907</v>
+        <v>7.80732297897339</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.32036209106445</v>
       </c>
       <c r="G738" t="n">
-        <v>7.78645896911621</v>
+        <v>7.78645849227905</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>9.64502716064453</v>
       </c>
       <c r="G740" t="n">
-        <v>8.05769062042236</v>
+        <v>8.057692527771</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>10.0196390151978</v>
       </c>
       <c r="G743" t="n">
-        <v>8.3706521987915</v>
+        <v>8.37065124511719</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.92473697662354</v>
       </c>
       <c r="G744" t="n">
-        <v>8.29136753082275</v>
+        <v>8.29136848449707</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.94971084594727</v>
       </c>
       <c r="G745" t="n">
-        <v>8.31223201751709</v>
+        <v>8.31223106384277</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.83483028411865</v>
       </c>
       <c r="G746" t="n">
-        <v>8.21625804901123</v>
+        <v>8.2162561416626</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.87978363037109</v>
       </c>
       <c r="G748" t="n">
-        <v>8.25381183624268</v>
+        <v>8.25381278991699</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.50017642974854</v>
       </c>
       <c r="G750" t="n">
-        <v>7.93667888641357</v>
+        <v>7.93667936325073</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.53514003753662</v>
       </c>
       <c r="G751" t="n">
-        <v>7.96588945388794</v>
+        <v>7.96588850021362</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>9.66001129150391</v>
       </c>
       <c r="G755" t="n">
-        <v>8.07021141052246</v>
+        <v>8.07020950317383</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.44523334503174</v>
       </c>
       <c r="G756" t="n">
-        <v>7.89077806472778</v>
+        <v>7.8907790184021</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.09559535980225</v>
       </c>
       <c r="G757" t="n">
-        <v>7.59868240356445</v>
+        <v>7.59868192672729</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.96073436737061</v>
       </c>
       <c r="G758" t="n">
-        <v>7.48601627349854</v>
+        <v>7.48601675033569</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.10058879852295</v>
       </c>
       <c r="G760" t="n">
-        <v>7.60285520553589</v>
+        <v>7.60285377502441</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.15553283691406</v>
       </c>
       <c r="G761" t="n">
-        <v>7.64875555038452</v>
+        <v>7.64875507354736</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>8.83086776733398</v>
       </c>
       <c r="G762" t="n">
-        <v>7.37752294540405</v>
+        <v>7.37752199172974</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.8858118057251</v>
       </c>
       <c r="G763" t="n">
-        <v>7.42342472076416</v>
+        <v>7.42342376708984</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>8.95074367523193</v>
       </c>
       <c r="G764" t="n">
-        <v>7.47767019271851</v>
+        <v>7.47767066955566</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.91578102111816</v>
       </c>
       <c r="G765" t="n">
-        <v>7.44846153259277</v>
+        <v>7.44846200942993</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>9.27041435241699</v>
       </c>
       <c r="G766" t="n">
-        <v>7.7447304725647</v>
+        <v>7.74473190307617</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.24044513702393</v>
       </c>
       <c r="G767" t="n">
-        <v>7.7196946144104</v>
+        <v>7.71969318389893</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>9.5850887298584</v>
       </c>
       <c r="G768" t="n">
-        <v>8.00761699676514</v>
+        <v>8.00761890411377</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G770" t="n">
-        <v>8.57929134368896</v>
+        <v>8.57929229736328</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.75990772247314</v>
       </c>
       <c r="G772" t="n">
-        <v>8.15366554260254</v>
+        <v>8.15366458892822</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.77988719940186</v>
       </c>
       <c r="G773" t="n">
-        <v>8.17035675048828</v>
+        <v>8.17035579681396</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.83982467651367</v>
       </c>
       <c r="G774" t="n">
-        <v>8.22043132781982</v>
+        <v>8.22042942047119</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>9.9197416305542</v>
       </c>
       <c r="G777" t="n">
-        <v>8.28719425201416</v>
+        <v>8.28719329833984</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.89476776123047</v>
       </c>
       <c r="G778" t="n">
-        <v>8.26632976531982</v>
+        <v>8.26633071899414</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.85480976104736</v>
       </c>
       <c r="G779" t="n">
-        <v>8.23294830322266</v>
+        <v>8.23294925689697</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G782" t="n">
-        <v>8.4541072845459</v>
+        <v>8.45410823822021</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G784" t="n">
-        <v>8.32892322540283</v>
+        <v>8.32892417907715</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>9.95970058441162</v>
       </c>
       <c r="G785" t="n">
-        <v>8.32057857513428</v>
+        <v>8.32057762145996</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>9.93972206115723</v>
       </c>
       <c r="G786" t="n">
-        <v>8.30388736724854</v>
+        <v>8.30388832092285</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>9.8997631072998</v>
       </c>
       <c r="G787" t="n">
-        <v>8.27050399780273</v>
+        <v>8.27050495147705</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>9.90475845336914</v>
       </c>
       <c r="G788" t="n">
-        <v>8.27467823028564</v>
+        <v>8.27467727661133</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.49018669128418</v>
       </c>
       <c r="G792" t="n">
-        <v>7.9283332824707</v>
+        <v>7.92833423614502</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>10.0196390151978</v>
       </c>
       <c r="G794" t="n">
-        <v>8.3706521987915</v>
+        <v>8.37065124511719</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G795" t="n">
-        <v>8.34561538696289</v>
+        <v>8.34561443328857</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G802" t="n">
-        <v>9.02995586395264</v>
+        <v>9.029953956604</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.838791847229</v>
       </c>
       <c r="G803" t="n">
-        <v>9.05499172210693</v>
+        <v>9.05499267578125</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G804" t="n">
-        <v>8.82966041564941</v>
+        <v>8.8296594619751</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>10.6290092468262</v>
       </c>
       <c r="G805" t="n">
-        <v>8.87973403930664</v>
+        <v>8.87973308563232</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G806" t="n">
-        <v>9.06333637237549</v>
+        <v>9.0633373260498</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>10.2593908309937</v>
       </c>
       <c r="G808" t="n">
-        <v>8.57094669342041</v>
+        <v>8.57094573974609</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>10.2394123077393</v>
       </c>
       <c r="G810" t="n">
-        <v>8.55425453186035</v>
+        <v>8.55425548553467</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>10.1794738769531</v>
       </c>
       <c r="G811" t="n">
-        <v>8.50417995452881</v>
+        <v>8.50418090820312</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>10.3692779541016</v>
       </c>
       <c r="G814" t="n">
-        <v>8.66274738311768</v>
+        <v>8.66274833679199</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G815" t="n">
-        <v>8.8880786895752</v>
+        <v>8.88807964324951</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G816" t="n">
-        <v>9.16348457336426</v>
+        <v>9.16348552703857</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>10.7788543701172</v>
       </c>
       <c r="G817" t="n">
-        <v>9.00491809844971</v>
+        <v>9.00491905212402</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G819" t="n">
-        <v>8.75454902648926</v>
+        <v>8.75455093383789</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G820" t="n">
-        <v>8.71282196044922</v>
+        <v>8.71282291412354</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G827" t="n">
-        <v>8.57929134368896</v>
+        <v>8.57929229736328</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>10.3293190002441</v>
       </c>
       <c r="G828" t="n">
-        <v>8.62936496734619</v>
+        <v>8.62936592102051</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>11.0785436630249</v>
       </c>
       <c r="G829" t="n">
-        <v>9.25528621673584</v>
+        <v>9.25528526306152</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06333637237549</v>
+        <v>9.0633373260498</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.7178831100464</v>
       </c>
       <c r="G838" t="n">
-        <v>9.78940677642822</v>
+        <v>9.78940582275391</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>11.5680379867554</v>
       </c>
       <c r="G839" t="n">
-        <v>9.66422176361084</v>
+        <v>9.66422080993652</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>11.8677282333374</v>
       </c>
       <c r="G841" t="n">
-        <v>9.91459083557129</v>
+        <v>9.91458988189697</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.6979036331177</v>
       </c>
       <c r="G844" t="n">
-        <v>9.77271461486816</v>
+        <v>9.77271556854248</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G845" t="n">
-        <v>9.79775142669678</v>
+        <v>9.79775238037109</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G846" t="n">
-        <v>9.76436901092529</v>
+        <v>9.76436805725098</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G848" t="n">
-        <v>9.53903770446777</v>
+        <v>9.53903579711914</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>11.0885343551636</v>
       </c>
       <c r="G849" t="n">
-        <v>9.26363277435303</v>
+        <v>9.26363372802734</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>11.3782339096069</v>
       </c>
       <c r="G851" t="n">
-        <v>9.50565433502197</v>
+        <v>9.50565528869629</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G853" t="n">
-        <v>9.06333637237549</v>
+        <v>9.0633373260498</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.2593908309937</v>
       </c>
       <c r="G854" t="n">
-        <v>8.57094669342041</v>
+        <v>8.57094573974609</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G857" t="n">
-        <v>8.59598255157471</v>
+        <v>8.59598159790039</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G859" t="n">
-        <v>8.51679134368896</v>
+        <v>8.51679229736328</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G860" t="n">
-        <v>8.52958679199219</v>
+        <v>8.52958583831787</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>9.9547061920166</v>
       </c>
       <c r="G861" t="n">
-        <v>8.49973297119141</v>
+        <v>8.49973201751709</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>9.59008312225342</v>
       </c>
       <c r="G862" t="n">
-        <v>8.18840312957764</v>
+        <v>8.188401222229</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.60007286071777</v>
       </c>
       <c r="G868" t="n">
-        <v>8.19693183898926</v>
+        <v>8.19693374633789</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>9.32036209106445</v>
       </c>
       <c r="G869" t="n">
-        <v>7.95810413360596</v>
+        <v>7.95810317993164</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>9.54013538360596</v>
       </c>
       <c r="G870" t="n">
-        <v>8.14575672149658</v>
+        <v>8.14575481414795</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>9.75990772247314</v>
       </c>
       <c r="G871" t="n">
-        <v>8.33340549468994</v>
+        <v>8.33340454101562</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>9.8647985458374</v>
       </c>
       <c r="G873" t="n">
-        <v>8.42296600341797</v>
+        <v>8.42296504974365</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G874" t="n">
-        <v>8.52958679199219</v>
+        <v>8.52958583831787</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G876" t="n">
-        <v>8.512526512146</v>
+        <v>8.51252746582031</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>9.93972206115723</v>
       </c>
       <c r="G877" t="n">
-        <v>8.48693943023682</v>
+        <v>8.48694038391113</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>9.93472671508789</v>
       </c>
       <c r="G878" t="n">
-        <v>8.48267269134521</v>
+        <v>8.48267364501953</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>9.8647985458374</v>
       </c>
       <c r="G879" t="n">
-        <v>8.42296600341797</v>
+        <v>8.42296504974365</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>10.2593908309937</v>
       </c>
       <c r="G883" t="n">
-        <v>8.75988578796387</v>
+        <v>8.75988388061523</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.0795774459839</v>
       </c>
       <c r="G884" t="n">
-        <v>8.60635185241699</v>
+        <v>8.60635280609131</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>9.92473697662354</v>
       </c>
       <c r="G885" t="n">
-        <v>8.47414398193359</v>
+        <v>8.47414302825928</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G886" t="n">
-        <v>8.52958679199219</v>
+        <v>8.52958583831787</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G887" t="n">
-        <v>8.51679134368896</v>
+        <v>8.51679229736328</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G891" t="n">
-        <v>9.02430152893066</v>
+        <v>9.02430248260498</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G892" t="n">
-        <v>9.06694889068604</v>
+        <v>9.06694793701172</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06694889068604</v>
+        <v>9.06694793701172</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G894" t="n">
-        <v>8.98165607452393</v>
+        <v>8.98165512084961</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>10.1694841384888</v>
       </c>
       <c r="G895" t="n">
-        <v>8.68311882019043</v>
+        <v>8.68311786651611</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.0296287536621</v>
       </c>
       <c r="G897" t="n">
-        <v>8.56370544433594</v>
+        <v>8.56370449066162</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G899" t="n">
-        <v>8.512526512146</v>
+        <v>8.51252746582031</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G900" t="n">
-        <v>8.52958679199219</v>
+        <v>8.52958583831787</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>9.6749963760376</v>
       </c>
       <c r="G901" t="n">
-        <v>8.26090526580811</v>
+        <v>8.26090431213379</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>9.63004207611084</v>
       </c>
       <c r="G902" t="n">
-        <v>8.22252082824707</v>
+        <v>8.22252178192139</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>9.66001129150391</v>
       </c>
       <c r="G903" t="n">
-        <v>8.2481107711792</v>
+        <v>8.24810981750488</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>10.3393087387085</v>
       </c>
       <c r="G906" t="n">
-        <v>8.82812118530273</v>
+        <v>8.82812213897705</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G907" t="n">
-        <v>8.76841449737549</v>
+        <v>8.7684154510498</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>10.3393087387085</v>
       </c>
       <c r="G908" t="n">
-        <v>8.82812118530273</v>
+        <v>8.82812213897705</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>9.31536674499512</v>
       </c>
       <c r="G910" t="n">
-        <v>7.95383882522583</v>
+        <v>7.95383930206299</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>9.26042366027832</v>
       </c>
       <c r="G911" t="n">
-        <v>7.90692663192749</v>
+        <v>7.90692567825317</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>9.30537796020508</v>
       </c>
       <c r="G912" t="n">
-        <v>7.94530963897705</v>
+        <v>7.94530916213989</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>9.06562614440918</v>
       </c>
       <c r="G913" t="n">
-        <v>7.74059963226318</v>
+        <v>7.74060106277466</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.85084819793701</v>
       </c>
       <c r="G914" t="n">
-        <v>7.55721426010132</v>
+        <v>7.55721378326416</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.67602825164795</v>
       </c>
       <c r="G915" t="n">
-        <v>7.40794563293457</v>
+        <v>7.40794467926025</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>8.71099185943604</v>
       </c>
       <c r="G916" t="n">
-        <v>7.43779850006104</v>
+        <v>7.43779945373535</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>8.69101333618164</v>
       </c>
       <c r="G917" t="n">
-        <v>7.42074060440063</v>
+        <v>7.42074012756348</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>8.411301612854</v>
       </c>
       <c r="G918" t="n">
-        <v>7.18191003799438</v>
+        <v>7.1819109916687</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>8.31140613555908</v>
       </c>
       <c r="G919" t="n">
-        <v>7.0966157913208</v>
+        <v>7.09661626815796</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>8.2264928817749</v>
       </c>
       <c r="G921" t="n">
-        <v>7.02411413192749</v>
+        <v>7.02411365509033</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>8.20651435852051</v>
       </c>
       <c r="G922" t="n">
-        <v>7.00705480575562</v>
+        <v>7.00705575942993</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>8.27644157409668</v>
       </c>
       <c r="G928" t="n">
-        <v>7.06676197052002</v>
+        <v>7.06676244735718</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>8.31140613555908</v>
       </c>
       <c r="G929" t="n">
-        <v>7.0966157913208</v>
+        <v>7.09661626815796</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>8.19152927398682</v>
       </c>
       <c r="G930" t="n">
-        <v>6.99426031112671</v>
+        <v>6.99426126480103</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>8.31140613555908</v>
       </c>
       <c r="G931" t="n">
-        <v>7.0966157913208</v>
+        <v>7.09661626815796</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>8.47623538970947</v>
       </c>
       <c r="G932" t="n">
-        <v>7.23735427856445</v>
+        <v>7.23735380172729</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>8.34636878967285</v>
       </c>
       <c r="G934" t="n">
-        <v>7.12646865844727</v>
+        <v>7.12646913528442</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>8.85084819793701</v>
       </c>
       <c r="G936" t="n">
-        <v>7.55721426010132</v>
+        <v>7.55721378326416</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>8.87582206726074</v>
       </c>
       <c r="G937" t="n">
-        <v>7.578537940979</v>
+        <v>7.57853841781616</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>9.18050670623779</v>
       </c>
       <c r="G939" t="n">
-        <v>7.83868885040283</v>
+        <v>7.83868837356567</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>9.36531639099121</v>
       </c>
       <c r="G940" t="n">
-        <v>7.99648809432983</v>
+        <v>7.99648857116699</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>9.4402379989624</v>
       </c>
       <c r="G941" t="n">
-        <v>8.06045913696289</v>
+        <v>8.06046009063721</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>9.51016616821289</v>
       </c>
       <c r="G943" t="n">
-        <v>8.12016487121582</v>
+        <v>8.12016582489014</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>9.36032104492188</v>
       </c>
       <c r="G944" t="n">
-        <v>7.99222183227539</v>
+        <v>7.99222278594971</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>9.33035182952881</v>
       </c>
       <c r="G945" t="n">
-        <v>7.96663331985474</v>
+        <v>7.96663427352905</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>9.36032104492188</v>
       </c>
       <c r="G947" t="n">
-        <v>7.99222183227539</v>
+        <v>7.99222278594971</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>8.96572875976562</v>
       </c>
       <c r="G948" t="n">
-        <v>7.65530347824097</v>
+        <v>7.65530395507812</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>8.79590511322021</v>
       </c>
       <c r="G949" t="n">
-        <v>7.51030158996582</v>
+        <v>7.51030206680298</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>8.66603946685791</v>
       </c>
       <c r="G950" t="n">
-        <v>7.39941692352295</v>
+        <v>7.39941644668579</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>8.81588363647461</v>
       </c>
       <c r="G951" t="n">
-        <v>7.52735996246338</v>
+        <v>7.52735900878906</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>8.92077541351318</v>
       </c>
       <c r="G952" t="n">
-        <v>7.61691999435425</v>
+        <v>7.61692094802856</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>8.93076515197754</v>
       </c>
       <c r="G953" t="n">
-        <v>7.62545013427734</v>
+        <v>7.62544965744019</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>8.7409610748291</v>
       </c>
       <c r="G954" t="n">
-        <v>7.46338748931885</v>
+        <v>7.46338796615601</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.55115795135498</v>
       </c>
       <c r="G955" t="n">
-        <v>7.30132722854614</v>
+        <v>7.30132579803467</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.43128204345703</v>
       </c>
       <c r="G956" t="n">
-        <v>7.19897127151489</v>
+        <v>7.19897079467773</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>8.49122047424316</v>
       </c>
       <c r="G957" t="n">
-        <v>7.25014877319336</v>
+        <v>7.2501482963562</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.48122978210449</v>
       </c>
       <c r="G958" t="n">
-        <v>7.24161815643311</v>
+        <v>7.24161911010742</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>8.33138465881348</v>
       </c>
       <c r="G959" t="n">
-        <v>7.11367511749268</v>
+        <v>7.11367464065552</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>8.51119899749756</v>
       </c>
       <c r="G960" t="n">
-        <v>7.26720762252808</v>
+        <v>7.26720714569092</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>8.94075489044189</v>
       </c>
       <c r="G962" t="n">
-        <v>7.63397979736328</v>
+        <v>7.6339807510376</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>8.92077541351318</v>
       </c>
       <c r="G963" t="n">
-        <v>7.61691999435425</v>
+        <v>7.61692094802856</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>9.12056922912598</v>
       </c>
       <c r="G965" t="n">
-        <v>7.787513256073</v>
+        <v>7.78751277923584</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>9.1605281829834</v>
       </c>
       <c r="G966" t="n">
-        <v>7.82163095474243</v>
+        <v>7.82163190841675</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>9.0156774520874</v>
       </c>
       <c r="G968" t="n">
-        <v>7.69795179367065</v>
+        <v>7.69795083999634</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>9.32535743713379</v>
       </c>
       <c r="G969" t="n">
-        <v>7.96236896514893</v>
+        <v>7.96236944198608</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>9.4002799987793</v>
       </c>
       <c r="G970" t="n">
-        <v>8.02634048461914</v>
+        <v>8.02634143829346</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>9.44523334503174</v>
       </c>
       <c r="G971" t="n">
-        <v>8.06472301483154</v>
+        <v>8.06472396850586</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>9.6749963760376</v>
       </c>
       <c r="G973" t="n">
-        <v>8.26090526580811</v>
+        <v>8.26090431213379</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.3892574310303</v>
       </c>
       <c r="G979" t="n">
-        <v>8.87076950073242</v>
+        <v>8.87077140808105</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G982" t="n">
-        <v>9.29724979400635</v>
+        <v>9.29724884033203</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.108512878418</v>
       </c>
       <c r="G983" t="n">
-        <v>9.48489952087402</v>
+        <v>9.48489856719971</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>10.7888441085815</v>
       </c>
       <c r="G985" t="n">
-        <v>9.21195316314697</v>
+        <v>9.21195411682129</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>10.5291118621826</v>
       </c>
       <c r="G988" t="n">
-        <v>8.99018383026123</v>
+        <v>8.99018287658691</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G989" t="n">
-        <v>9.16077518463135</v>
+        <v>9.16077613830566</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G991" t="n">
-        <v>9.06694889068604</v>
+        <v>9.06694793701172</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>10.7988338470459</v>
       </c>
       <c r="G992" t="n">
-        <v>9.22048377990723</v>
+        <v>9.22048282623291</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G995" t="n">
-        <v>9.53607749938965</v>
+        <v>9.53607845306396</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>11.128493309021</v>
       </c>
       <c r="G996" t="n">
-        <v>9.50196075439453</v>
+        <v>9.50195980072021</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>11.2283887863159</v>
       </c>
       <c r="G997" t="n">
-        <v>9.58725547790527</v>
+        <v>9.58725357055664</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>11.2383785247803</v>
       </c>
       <c r="G999" t="n">
-        <v>9.59578514099121</v>
+        <v>9.59578418731689</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>11.2084102630615</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.57019519805908</v>
+        <v>9.57019710540771</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>11.0186061859131</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.4081335067749</v>
+        <v>9.40813446044922</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>11.1584615707397</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.52754783630371</v>
+        <v>9.52754688262939</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.29724979400635</v>
+        <v>9.29724884033203</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.2631311416626</v>
+        <v>9.26313018798828</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>11.0585651397705</v>
       </c>
       <c r="G1021" t="n">
-        <v>9.44225120544434</v>
+        <v>9.44225215911865</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.0285959243774</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.41666316986084</v>
+        <v>9.41666221618652</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G1023" t="n">
-        <v>9.42519283294678</v>
+        <v>9.42519378662109</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.128493309021</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.50196075439453</v>
+        <v>9.50195980072021</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>11.1185026168823</v>
       </c>
       <c r="G1025" t="n">
-        <v>9.49343013763428</v>
+        <v>9.49342918395996</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>10.9087200164795</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.31430816650391</v>
+        <v>9.31430912017822</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.108512878418</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.48489952087402</v>
+        <v>9.48489856719971</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>10.9087200164795</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.31430816650391</v>
+        <v>9.31430912017822</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>10.5990400314331</v>
       </c>
       <c r="G1031" t="n">
-        <v>9.04989051818848</v>
+        <v>9.04989147186279</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>10.1694841384888</v>
       </c>
       <c r="G1033" t="n">
-        <v>8.68311882019043</v>
+        <v>8.68311786651611</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.94753551483154</v>
+        <v>8.94753646850586</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>10.7888441085815</v>
       </c>
       <c r="G1041" t="n">
-        <v>9.21195316314697</v>
+        <v>9.21195411682129</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.87930107116699</v>
+        <v>8.87929916381836</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.76841449737549</v>
+        <v>8.7684154510498</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>10.3492975234985</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.83664989471436</v>
+        <v>8.83665084838867</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G1045" t="n">
-        <v>9.17783546447754</v>
+        <v>9.17783451080322</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G1046" t="n">
-        <v>9.02430152893066</v>
+        <v>9.02430248260498</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.87930107116699</v>
+        <v>8.87929916381836</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G1048" t="n">
-        <v>9.1693058013916</v>
+        <v>9.16930484771729</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>10.4991426467896</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.9645938873291</v>
+        <v>8.96459484100342</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>10.3592882156372</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.84518146514893</v>
+        <v>8.84518051147461</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>9.56011390686035</v>
       </c>
       <c r="G1053" t="n">
-        <v>8.16281318664551</v>
+        <v>8.16281414031982</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>9.4951810836792</v>
       </c>
       <c r="G1054" t="n">
-        <v>8.10737228393555</v>
+        <v>8.10737133026123</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>9.23045539855957</v>
       </c>
       <c r="G1056" t="n">
-        <v>7.88133764266968</v>
+        <v>7.88133859634399</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>9.03066158294678</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.71074533462524</v>
+        <v>7.7107458114624</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.54116821289062</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.29279661178589</v>
+        <v>7.29279613494873</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.65604877471924</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.39088535308838</v>
+        <v>7.39088678359985</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.4612512588501</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.22455978393555</v>
+        <v>7.22456026077271</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>8.10661697387695</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.9217586517334</v>
+        <v>6.92175912857056</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.18153953552246</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.98573064804077</v>
+        <v>6.98573112487793</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>6.69307899475098</v>
       </c>
       <c r="G1068" t="n">
-        <v>5.71482276916504</v>
+        <v>5.7148232460022</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>7.46228313446045</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.37160062789917</v>
+        <v>6.37160015106201</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>8.10162162780762</v>
       </c>
       <c r="G1071" t="n">
-        <v>6.91749382019043</v>
+        <v>6.91749334335327</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>8.80089855194092</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.51456451416016</v>
+        <v>7.51456356048584</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>7.99673080444336</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.82793283462524</v>
+        <v>6.8279333114624</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>7.37237596511841</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.29483461380005</v>
+        <v>6.29483413696289</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>7.19256210327148</v>
       </c>
       <c r="G1077" t="n">
-        <v>6.14130163192749</v>
+        <v>6.14130210876465</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.7879810333252</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.79585409164429</v>
+        <v>5.79585361480713</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>6.66310977935791</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.68923425674438</v>
+        <v>5.68923377990723</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.3933892250061</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.45893621444702</v>
+        <v>5.45893573760986</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.23355388641357</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.32246160507202</v>
+        <v>5.32246112823486</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.3134708404541</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.39069843292236</v>
+        <v>5.39069747924805</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.69307899475098</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.71482276916504</v>
+        <v>5.7148232460022</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>6.633141040802</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.66364526748657</v>
+        <v>5.66364574432373</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.43334722518921</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.49305295944214</v>
+        <v>5.4930534362793</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6.75301694869995</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.76600074768066</v>
+        <v>5.76600027084351</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6.90286207199097</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.89394378662109</v>
+        <v>5.89394474029541</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6.89786720275879</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.88967943191528</v>
+        <v>5.88967895507812</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>7.50723695755005</v>
       </c>
       <c r="G1095" t="n">
-        <v>6.40998363494873</v>
+        <v>6.40998411178589</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>7.78694820404053</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.64881229400635</v>
+        <v>6.64881277084351</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>7.627112865448</v>
       </c>
       <c r="G1097" t="n">
-        <v>6.51233911514282</v>
+        <v>6.51233863830566</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>7.82191181182861</v>
       </c>
       <c r="G1098" t="n">
-        <v>6.67866563796997</v>
+        <v>6.67866611480713</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>7.75697898864746</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.62322378158569</v>
+        <v>6.62322330474854</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.3873610496521</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.3076286315918</v>
+        <v>6.30762910842896</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.38236618041992</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.30336427688599</v>
+        <v>6.30336380004883</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.2475061416626</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.18821573257446</v>
+        <v>6.1882152557373</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.0926661491394</v>
       </c>
       <c r="G1106" t="n">
-        <v>6.05600690841675</v>
+        <v>6.05600643157959</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.13262414932251</v>
       </c>
       <c r="G1110" t="n">
-        <v>6.09012460708618</v>
+        <v>6.09012413024902</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>7.28246879577637</v>
       </c>
       <c r="G1113" t="n">
-        <v>6.21806812286377</v>
+        <v>6.21806764602661</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>7.37237596511841</v>
       </c>
       <c r="G1114" t="n">
-        <v>6.29483461380005</v>
+        <v>6.29483413696289</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>8.15656566619873</v>
       </c>
       <c r="G1116" t="n">
-        <v>6.96440744400024</v>
+        <v>6.9644079208374</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>8.56114673614502</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.30985498428345</v>
+        <v>7.30985593795776</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>8.39631843566895</v>
       </c>
       <c r="G1118" t="n">
-        <v>7.16911792755127</v>
+        <v>7.16911745071411</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>8.39631843566895</v>
       </c>
       <c r="G1119" t="n">
-        <v>7.16911792755127</v>
+        <v>7.16911745071411</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>8.35136413574219</v>
       </c>
       <c r="G1120" t="n">
-        <v>7.13073396682739</v>
+        <v>7.13073348999023</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>8.56114673614502</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.30985498428345</v>
+        <v>7.30985593795776</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>8.65604877471924</v>
       </c>
       <c r="G1123" t="n">
-        <v>7.39088535308838</v>
+        <v>7.39088678359985</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>8.88081741333008</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.58280229568481</v>
+        <v>7.58280324935913</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>8.75095081329346</v>
       </c>
       <c r="G1125" t="n">
-        <v>7.47191762924194</v>
+        <v>7.47191858291626</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>8.49122047424316</v>
       </c>
       <c r="G1127" t="n">
-        <v>7.25014877319336</v>
+        <v>7.2501482963562</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>8.37633800506592</v>
       </c>
       <c r="G1129" t="n">
-        <v>7.15205812454224</v>
+        <v>7.15205764770508</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>8.27644157409668</v>
       </c>
       <c r="G1130" t="n">
-        <v>7.06676197052002</v>
+        <v>7.06676244735718</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>8.3713436126709</v>
       </c>
       <c r="G1131" t="n">
-        <v>7.14779376983643</v>
+        <v>7.14779329299927</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>8.17154979705811</v>
       </c>
       <c r="G1134" t="n">
-        <v>6.97720098495483</v>
+        <v>6.97720146179199</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>8.411301612854</v>
       </c>
       <c r="G1136" t="n">
-        <v>7.18191003799438</v>
+        <v>7.1819109916687</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>8.20651435852051</v>
       </c>
       <c r="G1137" t="n">
-        <v>7.00705480575562</v>
+        <v>7.00705575942993</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>8.20151901245117</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.00278997421265</v>
+        <v>7.0027904510498</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>8.411301612854</v>
       </c>
       <c r="G1140" t="n">
-        <v>7.18191003799438</v>
+        <v>7.1819109916687</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>8.26645183563232</v>
       </c>
       <c r="G1144" t="n">
-        <v>7.05823278427124</v>
+        <v>7.05823230743408</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>8.39132308959961</v>
       </c>
       <c r="G1145" t="n">
-        <v>7.16485214233398</v>
+        <v>7.16485261917114</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>8.56114673614502</v>
       </c>
       <c r="G1146" t="n">
-        <v>7.30985498428345</v>
+        <v>7.30985593795776</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>8.34137535095215</v>
       </c>
       <c r="G1147" t="n">
-        <v>7.12220525741577</v>
+        <v>7.12220478057861</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>8.14158058166504</v>
       </c>
       <c r="G1148" t="n">
-        <v>6.95161247253418</v>
+        <v>6.95161199569702</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>8.20151901245117</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.00278997421265</v>
+        <v>7.0027904510498</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>8.47124004364014</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.23308849334717</v>
+        <v>7.23308897018433</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>8.35136413574219</v>
       </c>
       <c r="G1153" t="n">
-        <v>7.13073396682739</v>
+        <v>7.13073348999023</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>8.16156005859375</v>
       </c>
       <c r="G1154" t="n">
-        <v>6.96867179870605</v>
+        <v>6.9686713218689</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>8.39132308959961</v>
       </c>
       <c r="G1156" t="n">
-        <v>7.16485214233398</v>
+        <v>7.16485261917114</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>8.17154979705811</v>
       </c>
       <c r="G1159" t="n">
-        <v>6.97720098495483</v>
+        <v>6.97720146179199</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>8.10162162780762</v>
       </c>
       <c r="G1160" t="n">
-        <v>6.91749382019043</v>
+        <v>6.91749334335327</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>8.10661697387695</v>
       </c>
       <c r="G1161" t="n">
-        <v>6.9217586517334</v>
+        <v>6.92175912857056</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>7.82191181182861</v>
       </c>
       <c r="G1162" t="n">
-        <v>6.67866563796997</v>
+        <v>6.67866611480713</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>7.53221082687378</v>
       </c>
       <c r="G1165" t="n">
-        <v>6.43130779266357</v>
+        <v>6.43130731582642</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>7.62211799621582</v>
       </c>
       <c r="G1166" t="n">
-        <v>6.5080738067627</v>
+        <v>6.50807428359985</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>7.69204616546631</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.56778144836426</v>
+        <v>6.56778192520142</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>7.64209794998169</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.52513360977173</v>
+        <v>6.52513313293457</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>8.0416841506958</v>
       </c>
       <c r="G1171" t="n">
-        <v>6.86631679534912</v>
+        <v>6.86631631851196</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>8.17154979705811</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.97720098495483</v>
+        <v>6.97720146179199</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>8.14158058166504</v>
       </c>
       <c r="G1176" t="n">
-        <v>6.95161247253418</v>
+        <v>6.95161199569702</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>7.98174619674683</v>
       </c>
       <c r="G1178" t="n">
-        <v>6.8151388168335</v>
+        <v>6.81513929367065</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>7.91181898117065</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.75543260574341</v>
+        <v>6.75543212890625</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>8.05666923522949</v>
       </c>
       <c r="G1180" t="n">
-        <v>6.87911176681519</v>
+        <v>6.87911128997803</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>8.07165336608887</v>
       </c>
       <c r="G1183" t="n">
-        <v>6.89190578460693</v>
+        <v>6.89190530776978</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>8.08164310455322</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.90043544769287</v>
+        <v>6.90043497085571</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>8.07165336608887</v>
       </c>
       <c r="G1185" t="n">
-        <v>6.89190578460693</v>
+        <v>6.89190530776978</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>7.99173593521118</v>
       </c>
       <c r="G1186" t="n">
-        <v>6.82366895675659</v>
+        <v>6.82366943359375</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>8.16156005859375</v>
       </c>
       <c r="G1187" t="n">
-        <v>6.96867179870605</v>
+        <v>6.9686713218689</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>8.38133335113525</v>
       </c>
       <c r="G1188" t="n">
-        <v>7.15632343292236</v>
+        <v>7.15632295608521</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>8.34137535095215</v>
       </c>
       <c r="G1189" t="n">
-        <v>7.12220525741577</v>
+        <v>7.12220478057861</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>8.37633800506592</v>
       </c>
       <c r="G1190" t="n">
-        <v>7.15205812454224</v>
+        <v>7.15205764770508</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>8.31140613555908</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.0966157913208</v>
+        <v>7.09661626815796</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>8.30641078948975</v>
       </c>
       <c r="G1192" t="n">
-        <v>7.09235191345215</v>
+        <v>7.09235048294067</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>8.53117847442627</v>
       </c>
       <c r="G1193" t="n">
-        <v>7.28426694869995</v>
+        <v>7.28426599502563</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>8.66104412078857</v>
       </c>
       <c r="G1194" t="n">
-        <v>7.39515113830566</v>
+        <v>7.39515161514282</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>9.08061027526855</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.75339412689209</v>
+        <v>7.75339460372925</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>8.67602825164795</v>
       </c>
       <c r="G1196" t="n">
-        <v>7.40794563293457</v>
+        <v>7.40794467926025</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>8.62607955932617</v>
       </c>
       <c r="G1197" t="n">
-        <v>7.3652982711792</v>
+        <v>7.36529731750488</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>8.27644157409668</v>
       </c>
       <c r="G1199" t="n">
-        <v>7.06676197052002</v>
+        <v>7.06676244735718</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>7.84189081192017</v>
       </c>
       <c r="G1200" t="n">
-        <v>6.69572496414185</v>
+        <v>6.695725440979</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>7.96176719665527</v>
       </c>
       <c r="G1201" t="n">
-        <v>6.79808044433594</v>
+        <v>6.79807996749878</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>8.19152927398682</v>
       </c>
       <c r="G1202" t="n">
-        <v>6.99426031112671</v>
+        <v>6.99426126480103</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>8.01671028137207</v>
       </c>
       <c r="G1203" t="n">
-        <v>6.84499311447144</v>
+        <v>6.84499263763428</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>8.05167388916016</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.8748459815979</v>
+        <v>6.87484693527222</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>8.32639026641846</v>
       </c>
       <c r="G1205" t="n">
-        <v>7.10941076278687</v>
+        <v>7.10940980911255</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>8.52118873596191</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.27573728561401</v>
+        <v>7.27573776245117</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>8.7409610748291</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.46338748931885</v>
+        <v>7.46338796615601</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>8.95573902130127</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.64677381515503</v>
+        <v>7.64677429199219</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>9.1105785369873</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.77898263931274</v>
+        <v>7.7789831161499</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>9.18050670623779</v>
       </c>
       <c r="G1212" t="n">
-        <v>7.83868885040283</v>
+        <v>7.83868837356567</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>9.12056922912598</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.787513256073</v>
+        <v>7.78751277923584</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>8.81088924407959</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.52309465408325</v>
+        <v>7.52309513092041</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>8.67103385925293</v>
       </c>
       <c r="G1216" t="n">
-        <v>7.4036808013916</v>
+        <v>7.40368175506592</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>8.6860179901123</v>
       </c>
       <c r="G1217" t="n">
-        <v>7.41647481918335</v>
+        <v>7.41647529602051</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>8.63107490539551</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.36956167221069</v>
+        <v>7.36956310272217</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>8.85584259033203</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.56147718429565</v>
+        <v>7.56147766113281</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>8.8858118057251</v>
       </c>
       <c r="G1220" t="n">
-        <v>7.58706760406494</v>
+        <v>7.58706617355347</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>9.07561492919922</v>
       </c>
       <c r="G1221" t="n">
-        <v>7.74912929534912</v>
+        <v>7.74912881851196</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>9.10058879852295</v>
       </c>
       <c r="G1222" t="n">
-        <v>7.77045297622681</v>
+        <v>7.77045154571533</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>9.28539752960205</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.92824935913086</v>
+        <v>7.92824983596802</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>9.73493385314941</v>
       </c>
       <c r="G1224" t="n">
-        <v>8.31208229064941</v>
+        <v>8.3120813369751</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>9.51016616821289</v>
       </c>
       <c r="G1225" t="n">
-        <v>8.12016487121582</v>
+        <v>8.12016582489014</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>8.56114673614502</v>
       </c>
       <c r="G1228" t="n">
-        <v>7.30985498428345</v>
+        <v>7.30985593795776</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>8.91078567504883</v>
       </c>
       <c r="G1229" t="n">
-        <v>7.60839033126831</v>
+        <v>7.60839128494263</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>8.7409610748291</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.46338748931885</v>
+        <v>7.46338796615601</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>8.86583232879639</v>
       </c>
       <c r="G1233" t="n">
-        <v>7.57000684738159</v>
+        <v>7.57000827789307</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>8.96073436737061</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.65103960037231</v>
+        <v>7.65103912353516</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>9.54013538360596</v>
       </c>
       <c r="G1235" t="n">
-        <v>8.14575672149658</v>
+        <v>8.14575481414795</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G1236" t="n">
-        <v>8.76841449737549</v>
+        <v>8.7684154510498</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>10.3492975234985</v>
       </c>
       <c r="G1237" t="n">
-        <v>8.83664989471436</v>
+        <v>8.83665084838867</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G1240" t="n">
-        <v>8.97312641143799</v>
+        <v>8.97312450408936</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G1241" t="n">
-        <v>8.92194747924805</v>
+        <v>8.92194652557373</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G1244" t="n">
-        <v>9.42519283294678</v>
+        <v>9.42519378662109</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>11.1584615707397</v>
       </c>
       <c r="G1245" t="n">
-        <v>9.52754783630371</v>
+        <v>9.52754688262939</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>11.1185026168823</v>
       </c>
       <c r="G1247" t="n">
-        <v>9.49343013763428</v>
+        <v>9.49342918395996</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>10.9187097549438</v>
       </c>
       <c r="G1249" t="n">
-        <v>9.32283687591553</v>
+        <v>9.32283782958984</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>10.7988338470459</v>
       </c>
       <c r="G1250" t="n">
-        <v>9.22048377990723</v>
+        <v>9.22048282623291</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G1251" t="n">
-        <v>9.29724979400635</v>
+        <v>9.29724884033203</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G1252" t="n">
-        <v>9.1693058013916</v>
+        <v>9.16930484771729</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G1253" t="n">
-        <v>9.06694889068604</v>
+        <v>9.06694793701172</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>10.5990400314331</v>
       </c>
       <c r="G1255" t="n">
-        <v>9.04989051818848</v>
+        <v>9.04989147186279</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>10.6589784622192</v>
       </c>
       <c r="G1258" t="n">
-        <v>9.10106945037842</v>
+        <v>9.1010684967041</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>10.5291118621826</v>
       </c>
       <c r="G1259" t="n">
-        <v>8.99018383026123</v>
+        <v>8.99018287658691</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G1261" t="n">
-        <v>9.29724979400635</v>
+        <v>9.29724884033203</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>10.7788543701172</v>
       </c>
       <c r="G1263" t="n">
-        <v>9.20342445373535</v>
+        <v>9.20342254638672</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>10.7888441085815</v>
       </c>
       <c r="G1264" t="n">
-        <v>9.21195316314697</v>
+        <v>9.21195411682129</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G1266" t="n">
-        <v>9.1693058013916</v>
+        <v>9.16930484771729</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>10.9087200164795</v>
       </c>
       <c r="G1267" t="n">
-        <v>9.31430816650391</v>
+        <v>9.31430912017822</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>10.7888441085815</v>
       </c>
       <c r="G1270" t="n">
-        <v>9.21195316314697</v>
+        <v>9.21195411682129</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>10.7189159393311</v>
       </c>
       <c r="G1271" t="n">
-        <v>9.15224456787109</v>
+        <v>9.15224647521973</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>10.688946723938</v>
       </c>
       <c r="G1272" t="n">
-        <v>9.1266565322876</v>
+        <v>9.12665748596191</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G1273" t="n">
-        <v>9.17783546447754</v>
+        <v>9.17783451080322</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>10.9087200164795</v>
       </c>
       <c r="G1274" t="n">
-        <v>9.31430816650391</v>
+        <v>9.31430912017822</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>10.7189159393311</v>
       </c>
       <c r="G1276" t="n">
-        <v>9.15224456787109</v>
+        <v>9.15224647521973</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G1280" t="n">
-        <v>8.78547382354736</v>
+        <v>8.78547286987305</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G1282" t="n">
-        <v>8.87930107116699</v>
+        <v>8.87929916381836</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G1283" t="n">
-        <v>8.98165607452393</v>
+        <v>8.98165512084961</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>10.7788543701172</v>
       </c>
       <c r="G1284" t="n">
-        <v>9.20342445373535</v>
+        <v>9.20342254638672</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>10.7888441085815</v>
       </c>
       <c r="G1285" t="n">
-        <v>9.21195316314697</v>
+        <v>9.21195411682129</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G1287" t="n">
-        <v>9.2631311416626</v>
+        <v>9.26313018798828</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>11.2283887863159</v>
       </c>
       <c r="G1290" t="n">
-        <v>9.58725547790527</v>
+        <v>9.58725357055664</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>11.0186061859131</v>
       </c>
       <c r="G1291" t="n">
-        <v>9.4081335067749</v>
+        <v>9.40813446044922</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>11.0186061859131</v>
       </c>
       <c r="G1293" t="n">
-        <v>9.4081335067749</v>
+        <v>9.40813446044922</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G1294" t="n">
-        <v>9.53607749938965</v>
+        <v>9.53607845306396</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G1295" t="n">
-        <v>9.29724979400635</v>
+        <v>9.29724884033203</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>11.128493309021</v>
       </c>
       <c r="G1297" t="n">
-        <v>9.50196075439453</v>
+        <v>9.50195980072021</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>11.278338432312</v>
       </c>
       <c r="G1299" t="n">
-        <v>9.62990379333496</v>
+        <v>9.62990283966064</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>11.4981098175049</v>
       </c>
       <c r="G1300" t="n">
-        <v>9.81755447387695</v>
+        <v>9.81755352020264</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G1306" t="n">
-        <v>9.42519283294678</v>
+        <v>9.42519378662109</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>10.7688636779785</v>
       </c>
       <c r="G1307" t="n">
-        <v>9.19489288330078</v>
+        <v>9.1948938369751</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>10.838791847229</v>
       </c>
       <c r="G1308" t="n">
-        <v>9.25460052490234</v>
+        <v>9.25460147857666</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>10.7588748931885</v>
       </c>
       <c r="G1310" t="n">
-        <v>9.18636512756348</v>
+        <v>9.18636417388916</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>11.1884307861328</v>
       </c>
       <c r="G1313" t="n">
-        <v>9.55313587188721</v>
+        <v>9.55313682556152</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G1316" t="n">
-        <v>8.91341686248779</v>
+        <v>8.91341781616211</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>10.5790605545044</v>
       </c>
       <c r="G1317" t="n">
-        <v>9.0328311920166</v>
+        <v>9.03283214569092</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G1318" t="n">
-        <v>8.98165607452393</v>
+        <v>8.98165512084961</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G1319" t="n">
-        <v>8.98165607452393</v>
+        <v>8.98165512084961</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G1322" t="n">
-        <v>9.02430152893066</v>
+        <v>9.02430248260498</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G1323" t="n">
-        <v>9.08400917053223</v>
+        <v>9.08401012420654</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>10.5291118621826</v>
       </c>
       <c r="G1325" t="n">
-        <v>8.99018383026123</v>
+        <v>8.99018287658691</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>10.5990400314331</v>
       </c>
       <c r="G1326" t="n">
-        <v>9.04989051818848</v>
+        <v>9.04989147186279</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G1327" t="n">
-        <v>9.06694889068604</v>
+        <v>9.06694793701172</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G1328" t="n">
-        <v>8.92194747924805</v>
+        <v>8.92194652557373</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>10.4691743850708</v>
       </c>
       <c r="G1329" t="n">
-        <v>8.93900680541992</v>
+        <v>8.93900585174561</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G1330" t="n">
-        <v>8.93047618865967</v>
+        <v>8.9304780960083</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.2631311416626</v>
+        <v>9.26313018798828</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>10.9187097549438</v>
       </c>
       <c r="G1336" t="n">
-        <v>9.32283687591553</v>
+        <v>9.32283782958984</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G1337" t="n">
-        <v>9.2631311416626</v>
+        <v>9.26313018798828</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G1338" t="n">
-        <v>9.02430152893066</v>
+        <v>9.02430248260498</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G1339" t="n">
-        <v>9.06694889068604</v>
+        <v>9.06694793701172</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G1340" t="n">
-        <v>8.98165607452393</v>
+        <v>8.98165512084961</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G1342" t="n">
-        <v>8.92194747924805</v>
+        <v>8.92194652557373</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G1343" t="n">
-        <v>9.02430152893066</v>
+        <v>9.02430248260498</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>10.4991426467896</v>
       </c>
       <c r="G1344" t="n">
-        <v>8.9645938873291</v>
+        <v>8.96459484100342</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>10.3892574310303</v>
       </c>
       <c r="G1345" t="n">
-        <v>8.87076950073242</v>
+        <v>8.87077140808105</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G1346" t="n">
-        <v>8.78547382354736</v>
+        <v>8.78547286987305</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G1348" t="n">
-        <v>8.93047618865967</v>
+        <v>8.9304780960083</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>10.9187097549438</v>
       </c>
       <c r="G1349" t="n">
-        <v>9.32283687591553</v>
+        <v>9.32283782958984</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>10.7888441085815</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.21195316314697</v>
+        <v>9.21195411682129</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>10.3492975234985</v>
       </c>
       <c r="G1353" t="n">
-        <v>8.83664989471436</v>
+        <v>8.83665084838867</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G1354" t="n">
-        <v>8.87930107116699</v>
+        <v>8.87929916381836</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>10.1395149230957</v>
       </c>
       <c r="G1355" t="n">
-        <v>8.65753078460693</v>
+        <v>8.65752983093262</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G1358" t="n">
-        <v>8.94753551483154</v>
+        <v>8.94753646850586</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G1359" t="n">
-        <v>9.02430152893066</v>
+        <v>9.02430248260498</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>10.3293190002441</v>
       </c>
       <c r="G1360" t="n">
-        <v>8.81959247589111</v>
+        <v>8.8195915222168</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>10.0695877075195</v>
       </c>
       <c r="G1361" t="n">
-        <v>8.59782218933105</v>
+        <v>8.59782314300537</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>10.1694841384888</v>
       </c>
       <c r="G1362" t="n">
-        <v>8.68311882019043</v>
+        <v>8.68311786651611</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G1364" t="n">
-        <v>8.92194747924805</v>
+        <v>8.92194652557373</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>10.3592882156372</v>
       </c>
       <c r="G1365" t="n">
-        <v>8.84518146514893</v>
+        <v>8.84518051147461</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>10.2194328308105</v>
       </c>
       <c r="G1368" t="n">
-        <v>8.7257661819458</v>
+        <v>8.72576713562012</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>10.25</v>
       </c>
       <c r="G1370" t="n">
-        <v>8.94421672821045</v>
+        <v>8.94421577453613</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1371" t="n">
-        <v>8.9354887008667</v>
+        <v>8.93548965454102</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G1372" t="n">
-        <v>9.17109298706055</v>
+        <v>9.17109394073486</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G1373" t="n">
-        <v>9.31071090698242</v>
+        <v>9.31070995330811</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1374" t="n">
-        <v>9.45905303955078</v>
+        <v>9.4590539932251</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G1385" t="n">
-        <v>9.43287658691406</v>
+        <v>9.43287563323975</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1387" t="n">
-        <v>9.2496280670166</v>
+        <v>9.24962711334229</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1390" t="n">
-        <v>9.26707935333252</v>
+        <v>9.26708030700684</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1391" t="n">
-        <v>9.37179279327393</v>
+        <v>9.37179183959961</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1395" t="n">
-        <v>9.31943702697754</v>
+        <v>9.31943607330322</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1396" t="n">
-        <v>9.31943702697754</v>
+        <v>9.31943607330322</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1399" t="n">
-        <v>9.37179279327393</v>
+        <v>9.37179183959961</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1400" t="n">
-        <v>9.28453254699707</v>
+        <v>9.28453159332275</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1401" t="n">
-        <v>9.2496280670166</v>
+        <v>9.24962711334229</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1402" t="n">
-        <v>9.10128498077393</v>
+        <v>9.10128402709961</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1408" t="n">
-        <v>9.28453254699707</v>
+        <v>9.28453159332275</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>9.07510662078857</v>
+        <v>9.07510566711426</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1415" t="n">
-        <v>9.61612319946289</v>
+        <v>9.61612415313721</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>9.61612319946289</v>
+        <v>9.61612415313721</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G1420" t="n">
-        <v>10.3927421569824</v>
+        <v>10.3927431106567</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G1421" t="n">
-        <v>10.3927421569824</v>
+        <v>10.3927431106567</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G1422" t="n">
-        <v>10.4450998306274</v>
+        <v>10.4450988769531</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1424" t="n">
-        <v>10.6370716094971</v>
+        <v>10.6370725631714</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>10.8203182220459</v>
+        <v>10.8203191757202</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1430" t="n">
-        <v>10.7156066894531</v>
+        <v>10.7156057357788</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1431" t="n">
-        <v>10.8203182220459</v>
+        <v>10.8203191757202</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.53235912323</v>
+        <v>10.5323581695557</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1434" t="n">
-        <v>10.733057975769</v>
+        <v>10.7330589294434</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1439" t="n">
-        <v>10.6108922958374</v>
+        <v>10.6108932495117</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1442" t="n">
-        <v>10.7417840957642</v>
+        <v>10.7417850494385</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G1443" t="n">
-        <v>10.6196184158325</v>
+        <v>10.6196193695068</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1446" t="n">
-        <v>10.5061807632446</v>
+        <v>10.5061817169189</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G1447" t="n">
-        <v>10.4450998306274</v>
+        <v>10.4450988769531</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G1451" t="n">
-        <v>10.4450998306274</v>
+        <v>10.4450988769531</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G1453" t="n">
-        <v>9.97389030456543</v>
+        <v>9.97389125823975</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>9.68593120574951</v>
+        <v>9.6859302520752</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1457" t="n">
-        <v>9.85172557830811</v>
+        <v>9.85172653198242</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>11</v>
       </c>
       <c r="G1460" t="n">
-        <v>9.59867095947266</v>
+        <v>9.59867000579834</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G1461" t="n">
-        <v>9.53758811950684</v>
+        <v>9.53758907318115</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1465" t="n">
-        <v>9.30198383331299</v>
+        <v>9.3019847869873</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1466" t="n">
-        <v>9.21472358703613</v>
+        <v>9.21472454071045</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1468" t="n">
-        <v>9.44160175323486</v>
+        <v>9.44160079956055</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G1469" t="n">
-        <v>9.53758811950684</v>
+        <v>9.53758907318115</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G1471" t="n">
-        <v>9.5724925994873</v>
+        <v>9.57249355316162</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1472" t="n">
-        <v>9.58121776580811</v>
+        <v>9.58121871948242</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1474" t="n">
-        <v>9.55504035949707</v>
+        <v>9.55503940582275</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.58994483947754</v>
+        <v>9.58994388580322</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>11</v>
       </c>
       <c r="G1478" t="n">
-        <v>9.59867095947266</v>
+        <v>9.59867000579834</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1480" t="n">
-        <v>9.88663005828857</v>
+        <v>9.88663101196289</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1481" t="n">
-        <v>9.86917877197266</v>
+        <v>9.86917781829834</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1485" t="n">
-        <v>9.85172557830811</v>
+        <v>9.85172653198242</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1486" t="n">
-        <v>10.0524253845215</v>
+        <v>10.0524263381958</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1488" t="n">
-        <v>10.2269477844238</v>
+        <v>10.2269468307495</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1491" t="n">
-        <v>10.017520904541</v>
+        <v>10.0175218582153</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1494" t="n">
-        <v>10.2269477844238</v>
+        <v>10.2269468307495</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1498" t="n">
-        <v>10.4014692306519</v>
+        <v>10.4014682769775</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1506" t="n">
-        <v>10.3054819107056</v>
+        <v>10.3054809570312</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G1507" t="n">
-        <v>10.4450998306274</v>
+        <v>10.4450988769531</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1508" t="n">
-        <v>10.4014692306519</v>
+        <v>10.4014682769775</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G1509" t="n">
-        <v>10.5672636032104</v>
+        <v>10.5672626495361</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1511" t="n">
-        <v>10.8377723693848</v>
+        <v>10.8377714157104</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1512" t="n">
-        <v>10.7417840957642</v>
+        <v>10.7417850494385</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G1514" t="n">
-        <v>10.6545238494873</v>
+        <v>10.654522895813</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1518" t="n">
-        <v>10.7417840957642</v>
+        <v>10.7417850494385</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G1520" t="n">
-        <v>10.5672636032104</v>
+        <v>10.5672626495361</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1527" t="n">
-        <v>11.1431846618652</v>
+        <v>11.1431837081909</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1529" t="n">
-        <v>11.4747734069824</v>
+        <v>11.4747753143311</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1536" t="n">
-        <v>11.0122919082642</v>
+        <v>11.0122928619385</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1541" t="n">
-        <v>10.5236339569092</v>
+        <v>10.5236330032349</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G1542" t="n">
-        <v>10.043701171875</v>
+        <v>10.0437002182007</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1543" t="n">
-        <v>10.0524253845215</v>
+        <v>10.0524263381958</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1544" t="n">
-        <v>10.2269477844238</v>
+        <v>10.2269468307495</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G1548" t="n">
-        <v>10.4450998306274</v>
+        <v>10.4450988769531</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1555" t="n">
-        <v>10.3316593170166</v>
+        <v>10.3316602706909</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1556" t="n">
-        <v>10.2269477844238</v>
+        <v>10.2269468307495</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1565" t="n">
-        <v>9.2496280670166</v>
+        <v>9.24962711334229</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1566" t="n">
-        <v>9.44160175323486</v>
+        <v>9.44160079956055</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1567" t="n">
-        <v>9.2496280670166</v>
+        <v>9.24962711334229</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G1568" t="n">
-        <v>9.1885461807251</v>
+        <v>9.18854522705078</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>10.25</v>
       </c>
       <c r="G1569" t="n">
-        <v>8.94421672821045</v>
+        <v>8.94421577453613</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1572" t="n">
-        <v>7.80110025405884</v>
+        <v>7.801100730896</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1573" t="n">
-        <v>7.9319920539856</v>
+        <v>7.93199300765991</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>8.25485610961914</v>
+        <v>8.25485706329346</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1575" t="n">
-        <v>7.97562313079834</v>
+        <v>7.9756236076355</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>8.76969432830811</v>
+        <v>8.76969528198242</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G1583" t="n">
-        <v>8.92676258087158</v>
+        <v>8.9267635345459</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1584" t="n">
-        <v>8.88313388824463</v>
+        <v>8.88313293457031</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G1587" t="n">
-        <v>8.66061973571777</v>
+        <v>8.66061878204346</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G1589" t="n">
-        <v>8.99657249450684</v>
+        <v>8.99657344818115</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1590" t="n">
-        <v>8.83077716827393</v>
+        <v>8.83077621459961</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G1592" t="n">
-        <v>8.78714656829834</v>
+        <v>8.78714561462402</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1593" t="n">
-        <v>8.58644771575928</v>
+        <v>8.58644676208496</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G1594" t="n">
-        <v>8.20686340332031</v>
+        <v>8.206862449646</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G1600" t="n">
-        <v>8.11960315704346</v>
+        <v>8.11960220336914</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G1604" t="n">
-        <v>8.46864604949951</v>
+        <v>8.4686450958252</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1609" t="n">
-        <v>8.37702178955078</v>
+        <v>8.3770227432251</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G1610" t="n">
-        <v>8.20686340332031</v>
+        <v>8.206862449646</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G1611" t="n">
-        <v>8.25922107696533</v>
+        <v>8.25922012329102</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1613" t="n">
-        <v>7.95817041397095</v>
+        <v>7.95816993713379</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1614" t="n">
-        <v>8.02361488342285</v>
+        <v>8.02361679077148</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1615" t="n">
-        <v>7.80110025405884</v>
+        <v>7.801100730896</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.90145111083984</v>
+        <v>7.90145063400269</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1618" t="n">
-        <v>9.2496280670166</v>
+        <v>9.24962711334229</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1619" t="n">
-        <v>9.38924503326416</v>
+        <v>9.38924598693848</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1624" t="n">
-        <v>9.30198383331299</v>
+        <v>9.3019847869873</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1627" t="n">
-        <v>9.36465358734131</v>
+        <v>9.36465454101562</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G1628" t="n">
-        <v>9.60638046264648</v>
+        <v>9.60637950897217</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1629" t="n">
-        <v>9.77648258209229</v>
+        <v>9.7764835357666</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1633" t="n">
-        <v>9.75857830047607</v>
+        <v>9.75857734680176</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G1635" t="n">
-        <v>9.78543663024902</v>
+        <v>9.78543758392334</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G1639" t="n">
-        <v>9.37360668182373</v>
+        <v>9.37360763549805</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G1643" t="n">
-        <v>8.6260461807251</v>
+        <v>8.62604522705078</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G1647" t="n">
-        <v>8.78272247314453</v>
+        <v>8.78272151947021</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>8.42908477783203</v>
+        <v>8.42908382415771</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1651" t="n">
-        <v>8.53204250335693</v>
+        <v>8.53204154968262</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1656" t="n">
-        <v>8.07544803619385</v>
+        <v>8.07544708251953</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1657" t="n">
-        <v>8.12916374206543</v>
+        <v>8.12916469573975</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1658" t="n">
-        <v>8.56337547302246</v>
+        <v>8.56337642669678</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G1661" t="n">
-        <v>8.64395141601562</v>
+        <v>8.64395236968994</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1662" t="n">
-        <v>8.57680606842041</v>
+        <v>8.57680511474609</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1663" t="n">
-        <v>8.37089252471924</v>
+        <v>8.37089157104492</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>9.625</v>
       </c>
       <c r="G1672" t="n">
-        <v>8.61709308624268</v>
+        <v>8.61709213256836</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1683" t="n">
-        <v>9.48999404907227</v>
+        <v>9.48999309539795</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>10.5</v>
       </c>
       <c r="G1685" t="n">
-        <v>9.40046501159668</v>
+        <v>9.40046405792236</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G1688" t="n">
-        <v>8.96177673339844</v>
+        <v>8.96177768707275</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G1693" t="n">
-        <v>8.35746192932129</v>
+        <v>8.35746288299561</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1697" t="n">
-        <v>8.15602207183838</v>
+        <v>8.15602111816406</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G1700" t="n">
-        <v>7.90086650848389</v>
+        <v>7.9008674621582</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1706" t="n">
-        <v>8.54994678497314</v>
+        <v>8.54994773864746</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1719" t="n">
-        <v>7.75314617156982</v>
+        <v>7.75314569473267</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G1720" t="n">
-        <v>8.08887577056885</v>
+        <v>8.08887672424316</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1721" t="n">
-        <v>7.99487257003784</v>
+        <v>7.99487352371216</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1722" t="n">
-        <v>8.11125946044922</v>
+        <v>8.1112585067749</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1731" t="n">
-        <v>8.67081069946289</v>
+        <v>8.67080974578857</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>10.5643320083618</v>
+        <v>10.5643329620361</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1748" t="n">
-        <v>10.4300403594971</v>
+        <v>10.4300394058228</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G1754" t="n">
-        <v>10.0003042221069</v>
+        <v>10.0003051757812</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1759" t="n">
-        <v>9.77648258209229</v>
+        <v>9.7764835357666</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G1761" t="n">
-        <v>10.0003042221069</v>
+        <v>10.0003051757812</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1765" t="n">
-        <v>9.80334281921387</v>
+        <v>9.80334186553955</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1766" t="n">
-        <v>9.63323879241943</v>
+        <v>9.63323974609375</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1771" t="n">
-        <v>9.58847427368164</v>
+        <v>9.58847522735596</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G1773" t="n">
-        <v>9.39151287078857</v>
+        <v>9.39151191711426</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1777" t="n">
-        <v>9.22140884399414</v>
+        <v>9.22140979766846</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>9.3557014465332</v>
+        <v>9.35570049285889</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1782" t="n">
-        <v>9.3557014465332</v>
+        <v>9.35570049285889</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G1783" t="n">
-        <v>9.39151287078857</v>
+        <v>9.39151191711426</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1787" t="n">
-        <v>9.80334281921387</v>
+        <v>9.80334186553955</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1795" t="n">
-        <v>10.3852767944336</v>
+        <v>10.3852758407593</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G1802" t="n">
-        <v>10.6270027160645</v>
+        <v>10.6270017623901</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1807" t="n">
-        <v>11.9520215988159</v>
+        <v>11.9520206451416</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1810" t="n">
-        <v>11.6565780639648</v>
+        <v>11.6565771102905</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1813" t="n">
-        <v>11.6565780639648</v>
+        <v>11.6565771102905</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1818" t="n">
-        <v>11.8714447021484</v>
+        <v>11.8714456558228</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1819" t="n">
-        <v>11.9520215988159</v>
+        <v>11.9520206451416</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G1822" t="n">
-        <v>12.5070953369141</v>
+        <v>12.5070962905884</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1823" t="n">
-        <v>13.3486614227295</v>
+        <v>13.3486604690552</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1834" t="n">
-        <v>11.9520215988159</v>
+        <v>11.9520206451416</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1836" t="n">
-        <v>11.8356332778931</v>
+        <v>11.8356342315674</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G1841" t="n">
-        <v>11.9878330230713</v>
+        <v>11.987832069397</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1843" t="n">
-        <v>11.6655302047729</v>
+        <v>11.6655292510986</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1846" t="n">
-        <v>11.9520215988159</v>
+        <v>11.9520206451416</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G1849" t="n">
-        <v>12.4175662994385</v>
+        <v>12.4175672531128</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>12.2206048965454</v>
+        <v>12.2206039428711</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G1854" t="n">
-        <v>11.9878330230713</v>
+        <v>11.987832069397</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1864" t="n">
-        <v>11.8714447021484</v>
+        <v>11.8714456558228</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1874" t="n">
-        <v>12.8920669555664</v>
+        <v>12.8920660018921</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1875" t="n">
-        <v>12.8114929199219</v>
+        <v>12.8114919662476</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>12.8473033905029</v>
+        <v>12.8473024368286</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1878" t="n">
-        <v>12.9368314743042</v>
+        <v>12.9368305206299</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>10.0200004577637</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>367341</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>10.3900003433228</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>10.0100002288818</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>10.0100002288818</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>9.86999988555908</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>10.039999961853</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>329234</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>10.3299999237061</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>10.0799999237061</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>10.2799997329712</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>635124</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>10.6899995803833</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>10.1999998092651</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>10.1700000762939</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>600825</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>10.0200004577637</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>9.76500034332275</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>10.0200004577637</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>10.0200004577637</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>9.82999992370605</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>208267</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>9.91499996185303</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>562563</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>10.1300001144409</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>9.90999984741211</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>10.0299997329712</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>9.9399995803833</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
